--- a/Exams/Semester 2/Physics/VPV/Data.xlsx
+++ b/Exams/Semester 2/Physics/VPV/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mihso\Documents\Study-data\Exams\Semester 2\Physics\VPV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0259C0A7-4F4F-4AB8-815D-635A73D19F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970BE0F1-967D-494E-B08D-3551D05BDEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,7 +853,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
@@ -1050,11 +1050,11 @@
         <v>5.0599999999999996</v>
       </c>
       <c r="I9">
-        <f t="shared" ref="I9:I11" si="0">H9/2</f>
+        <f t="shared" ref="I9:I12" si="0">H9/2</f>
         <v>2.5299999999999998</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" ref="J9:J11" si="1">I9*G9</f>
+        <f t="shared" ref="J9:J12" si="1">I9*G9</f>
         <v>74.938599999999994</v>
       </c>
     </row>
@@ -1102,6 +1102,25 @@
       <c r="J11" s="8">
         <f t="shared" si="1"/>
         <v>77.248599999999982</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="F12" s="8">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="G12" s="8">
+        <v>30.13</v>
+      </c>
+      <c r="H12" s="8">
+        <v>5.57</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="1"/>
+        <v>83.912050000000008</v>
       </c>
     </row>
   </sheetData>

--- a/Exams/Semester 2/Physics/VPV/Data.xlsx
+++ b/Exams/Semester 2/Physics/VPV/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mihso\Documents\Study-data\Exams\Semester 2\Physics\VPV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970BE0F1-967D-494E-B08D-3551D05BDEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C04A9B-08D9-491B-BE0D-0D53EC65FEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Оборудование" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="22">
   <si>
     <t>Радиус капли</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Быстро</t>
   </si>
   <si>
-    <t>Rугл, мм</t>
-  </si>
-  <si>
     <t>R, мм</t>
   </si>
   <si>
@@ -121,39 +118,30 @@
     <t>dc, мм</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>σR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Liberation Sans"/>
-      </rPr>
-      <t>, мм</t>
-    </r>
-  </si>
-  <si>
     <t>rc, мм</t>
   </si>
   <si>
     <t>lrc, мм^2</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Stdev</t>
+  </si>
+  <si>
+    <t>Relative</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -249,7 +237,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,6 +304,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -341,7 +341,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
@@ -362,8 +362,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="11"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1"/>
@@ -375,8 +376,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="14" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="15" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="13" borderId="0" xfId="20" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="13" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="21">
     <cellStyle name="Accent" xfId="7" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Accent 1" xfId="8" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Accent 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -393,6 +402,7 @@
     <cellStyle name="Neutral" xfId="5" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
     <cellStyle name="Note" xfId="6" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="20" builtinId="5"/>
     <cellStyle name="Result" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="Status" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Text" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
@@ -741,10 +751,10 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -853,7 +863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
@@ -875,15 +885,18 @@
         <v>7</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -915,8 +928,12 @@
         <v>5.32</v>
       </c>
       <c r="I2" s="8">
-        <f>STDEV(F2:F5)</f>
-        <v>1.0808754168111405</v>
+        <f>H2/2</f>
+        <v>2.66</v>
+      </c>
+      <c r="J2" s="8">
+        <f>I2*G2</f>
+        <v>91.238</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -933,6 +950,14 @@
       <c r="H3" s="8">
         <v>5.57</v>
       </c>
+      <c r="I3" s="8">
+        <f t="shared" ref="I3:I5" si="0">H3/2</f>
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="J3" s="8">
+        <f t="shared" ref="J3:J5" si="1">I3*G3</f>
+        <v>72.939150000000012</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="7"/>
@@ -948,6 +973,14 @@
       <c r="H4" s="8">
         <v>5.32</v>
       </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>2.66</v>
+      </c>
+      <c r="J4" s="8">
+        <f t="shared" si="1"/>
+        <v>79.108400000000003</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="7"/>
@@ -963,164 +996,1386 @@
       <c r="H5" s="8">
         <v>5.57</v>
       </c>
+      <c r="I5" s="8">
+        <f t="shared" si="0"/>
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="1"/>
+        <v>75.055750000000003</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="E6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="11">
+        <f>AVERAGE(F2:F5)</f>
+        <v>9.2125000000000004</v>
+      </c>
+      <c r="G6" s="11">
+        <f t="shared" ref="G6:J6" si="2">AVERAGE(G2:G5)</f>
+        <v>29.294999999999998</v>
+      </c>
+      <c r="H6" s="11">
+        <f t="shared" si="2"/>
+        <v>5.4450000000000003</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="2"/>
+        <v>2.7225000000000001</v>
+      </c>
+      <c r="J6" s="11">
+        <f t="shared" si="2"/>
+        <v>79.585324999999997</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="13.8">
-      <c r="B7" s="9" t="s">
+      <c r="E7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="12">
+        <f>STDEV(F2:F5)</f>
+        <v>1.0808754168111405</v>
+      </c>
+      <c r="G7" s="12">
+        <f t="shared" ref="G7:J7" si="3">STDEV(G2:G5)</f>
+        <v>3.6691552161226486</v>
+      </c>
+      <c r="H7" s="12">
+        <f t="shared" si="3"/>
+        <v>0.14433756729740643</v>
+      </c>
+      <c r="I7" s="12">
+        <f t="shared" si="3"/>
+        <v>7.2168783648703216E-2</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="3"/>
+        <v>8.1792620678253485</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="E8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="16">
+        <f>F7/F6</f>
+        <v>0.11732704660093791</v>
+      </c>
+      <c r="G8" s="16">
+        <f>G7/G6</f>
+        <v>0.12524851394854578</v>
+      </c>
+      <c r="H8" s="16">
+        <f>H7/H6</f>
+        <v>2.6508276822296863E-2</v>
+      </c>
+      <c r="I8" s="16">
+        <f>I7/I6</f>
+        <v>2.6508276822296863E-2</v>
+      </c>
+      <c r="J8" s="16">
+        <f>J7/J6</f>
+        <v>0.10277349584016084</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.8">
+      <c r="B9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="H9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="7">
+      <c r="J9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="8">
         <v>45</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C10" s="8">
         <v>4.5</v>
       </c>
-      <c r="D8" s="7">
-        <f>B8-C8</f>
+      <c r="D10" s="8">
+        <f>B10-C10</f>
         <v>40.5</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E10" s="8">
         <f>Оборудование!$I$2</f>
         <v>1</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F10" s="8">
         <v>9.36</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G10" s="8">
         <v>33.17</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H10" s="8">
         <v>5.32</v>
       </c>
-      <c r="I8">
-        <f>H8/2</f>
+      <c r="I10" s="8">
+        <f>H10/2</f>
         <v>2.66</v>
       </c>
-      <c r="J8" s="8">
-        <f>I8*G8</f>
+      <c r="J10" s="8">
+        <f>I10*G10</f>
         <v>88.232200000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8">
+    <row r="11" spans="1:10">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8">
         <v>9.36</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G11" s="8">
         <v>29.62</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H11" s="8">
         <v>5.0599999999999996</v>
       </c>
-      <c r="I9">
-        <f t="shared" ref="I9:I12" si="0">H9/2</f>
+      <c r="I11" s="8">
+        <f t="shared" ref="I11:I14" si="4">H11/2</f>
         <v>2.5299999999999998</v>
       </c>
-      <c r="J9" s="8">
-        <f t="shared" ref="J9:J12" si="1">I9*G9</f>
+      <c r="J11" s="8">
+        <f t="shared" ref="J11:J14" si="5">I11*G11</f>
         <v>74.938599999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8">
+    <row r="12" spans="1:10">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8">
         <v>8.86</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G12" s="8">
         <v>28.11</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H12" s="8">
         <v>5.82</v>
       </c>
-      <c r="I10">
-        <f t="shared" si="0"/>
+      <c r="I12" s="8">
+        <f t="shared" si="4"/>
         <v>2.91</v>
       </c>
-      <c r="J10" s="8">
-        <f t="shared" si="1"/>
+      <c r="J12" s="8">
+        <f t="shared" si="5"/>
         <v>81.8001</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8">
+    <row r="13" spans="1:10">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8">
         <v>10.63</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G13" s="8">
         <v>32.119999999999997</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H13" s="8">
         <v>4.8099999999999996</v>
       </c>
-      <c r="I11">
-        <f t="shared" si="0"/>
+      <c r="I13" s="8">
+        <f t="shared" si="4"/>
         <v>2.4049999999999998</v>
       </c>
-      <c r="J11" s="8">
-        <f t="shared" si="1"/>
+      <c r="J13" s="8">
+        <f t="shared" si="5"/>
         <v>77.248599999999982</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="F12" s="8">
+    <row r="14" spans="1:10">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8">
         <v>10.119999999999999</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G14" s="8">
         <v>30.13</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H14" s="8">
         <v>5.57</v>
       </c>
-      <c r="I12">
-        <f t="shared" si="0"/>
+      <c r="I14" s="8">
+        <f t="shared" si="4"/>
         <v>2.7850000000000001</v>
       </c>
-      <c r="J12" s="8">
-        <f t="shared" si="1"/>
+      <c r="J14" s="8">
+        <f t="shared" si="5"/>
         <v>83.912050000000008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="11">
+        <f>AVERAGE(F10:F14)</f>
+        <v>9.6660000000000004</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" ref="G15:J15" si="6">AVERAGE(G10:G14)</f>
+        <v>30.630000000000003</v>
+      </c>
+      <c r="H15" s="11">
+        <f t="shared" si="6"/>
+        <v>5.3159999999999998</v>
+      </c>
+      <c r="I15" s="11">
+        <f t="shared" si="6"/>
+        <v>2.6579999999999999</v>
+      </c>
+      <c r="J15" s="11">
+        <f t="shared" si="6"/>
+        <v>81.226309999999984</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.8">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="12">
+        <f>STDEV(F10:F14)</f>
+        <v>0.70219655367995126</v>
+      </c>
+      <c r="G16" s="12">
+        <f t="shared" ref="G16:J16" si="7">STDEV(G10:G14)</f>
+        <v>2.0181798730539358</v>
+      </c>
+      <c r="H16" s="12">
+        <f t="shared" si="7"/>
+        <v>0.40003749824235257</v>
+      </c>
+      <c r="I16" s="12">
+        <f t="shared" si="7"/>
+        <v>0.20001874912117629</v>
+      </c>
+      <c r="J16" s="12">
+        <f t="shared" si="7"/>
+        <v>5.2910869131965779</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="E17" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="16">
+        <f>F16/F15</f>
+        <v>7.2646032865709836E-2</v>
+      </c>
+      <c r="G17" s="16">
+        <f t="shared" ref="G17:J17" si="8">G16/G15</f>
+        <v>6.5888993570157872E-2</v>
+      </c>
+      <c r="H17" s="16">
+        <f t="shared" si="8"/>
+        <v>7.5251598615942925E-2</v>
+      </c>
+      <c r="I17" s="16">
+        <f t="shared" si="8"/>
+        <v>7.5251598615942925E-2</v>
+      </c>
+      <c r="J17" s="16">
+        <f t="shared" si="8"/>
+        <v>6.5140062538807678E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="13.8">
+      <c r="B18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="8">
+        <v>40</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D19" s="8">
+        <f>B19-C19</f>
+        <v>35.5</v>
+      </c>
+      <c r="E19" s="8">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="G19" s="8">
+        <v>30.23</v>
+      </c>
+      <c r="H19" s="8">
+        <v>4.78</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" ref="I19:I24" si="9">H19/2</f>
+        <v>2.39</v>
+      </c>
+      <c r="J19" s="8">
+        <f>I19*G19</f>
+        <v>72.249700000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="G20" s="8">
+        <v>27.78</v>
+      </c>
+      <c r="H20" s="8">
+        <v>4.91</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="9"/>
+        <v>2.4550000000000001</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" ref="J20:J24" si="10">I20*G20</f>
+        <v>68.1999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="G21">
+        <v>27.52</v>
+      </c>
+      <c r="H21" s="8">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="9"/>
+        <v>2.1949999999999998</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="10"/>
+        <v>60.406399999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8">
+        <v>8.76</v>
+      </c>
+      <c r="G22" s="8">
+        <v>30.88</v>
+      </c>
+      <c r="H22" s="8">
+        <v>4.91</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="9"/>
+        <v>2.4550000000000001</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="10"/>
+        <v>75.810400000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8">
+        <v>8.76</v>
+      </c>
+      <c r="G23" s="8">
+        <v>29.2</v>
+      </c>
+      <c r="H23" s="8">
+        <v>4.78</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="9"/>
+        <v>2.39</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="10"/>
+        <v>69.787999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8">
+        <v>9.15</v>
+      </c>
+      <c r="G24" s="8">
+        <v>31.52</v>
+      </c>
+      <c r="H24" s="8">
+        <v>4.78</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="9"/>
+        <v>2.39</v>
+      </c>
+      <c r="J24" s="8">
+        <f t="shared" si="10"/>
+        <v>75.332800000000006</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="11">
+        <f>AVERAGE(F19:F24)</f>
+        <v>8.8466666666666658</v>
+      </c>
+      <c r="G25" s="11">
+        <f t="shared" ref="G25:J25" si="11">AVERAGE(G19:G24)</f>
+        <v>29.521666666666665</v>
+      </c>
+      <c r="H25" s="11">
+        <f t="shared" si="11"/>
+        <v>4.7583333333333337</v>
+      </c>
+      <c r="I25" s="11">
+        <f t="shared" si="11"/>
+        <v>2.3791666666666669</v>
+      </c>
+      <c r="J25" s="11">
+        <f t="shared" si="11"/>
+        <v>70.297866666666678</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="13.8">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="12">
+        <f>STDEV(F19:F24)</f>
+        <v>0.30395175055700296</v>
+      </c>
+      <c r="G26" s="12">
+        <f t="shared" ref="G26:J26" si="12">STDEV(G19:G24)</f>
+        <v>1.6421743715777157</v>
+      </c>
+      <c r="H26" s="12">
+        <f t="shared" si="12"/>
+        <v>0.19135481877043689</v>
+      </c>
+      <c r="I26" s="12">
+        <f t="shared" si="12"/>
+        <v>9.5677409385218445E-2</v>
+      </c>
+      <c r="J26" s="12">
+        <f t="shared" si="12"/>
+        <v>5.6929916872121549</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="16">
+        <f>F26/F25</f>
+        <v>3.4357771351582855E-2</v>
+      </c>
+      <c r="G27" s="16">
+        <f t="shared" ref="G27:J27" si="13">G26/G25</f>
+        <v>5.5626072542574914E-2</v>
+      </c>
+      <c r="H27" s="16">
+        <f t="shared" si="13"/>
+        <v>4.021467294650162E-2</v>
+      </c>
+      <c r="I27" s="16">
+        <f t="shared" si="13"/>
+        <v>4.021467294650162E-2</v>
+      </c>
+      <c r="J27" s="16">
+        <f t="shared" si="13"/>
+        <v>8.0983847123082264E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" ht="13.8">
+      <c r="B28" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="8">
+        <v>35</v>
+      </c>
+      <c r="C29" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D29" s="8">
+        <f>B29-C29</f>
+        <v>30.5</v>
+      </c>
+      <c r="E29" s="8">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="G29" s="8">
+        <v>25.71</v>
+      </c>
+      <c r="H29" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="I29" s="8">
+        <f>H29/2</f>
+        <v>1.87</v>
+      </c>
+      <c r="J29" s="8">
+        <f>I29*G29</f>
+        <v>48.077700000000007</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8">
+        <v>8.89</v>
+      </c>
+      <c r="G30" s="8">
+        <v>26.36</v>
+      </c>
+      <c r="H30" s="8">
+        <v>4</v>
+      </c>
+      <c r="I30" s="8">
+        <f t="shared" ref="I30:I36" si="14">H30/2</f>
+        <v>2</v>
+      </c>
+      <c r="J30" s="8">
+        <f t="shared" ref="J30:J36" si="15">I30*G30</f>
+        <v>52.72</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8">
+        <v>9.15</v>
+      </c>
+      <c r="G31" s="8">
+        <v>25.97</v>
+      </c>
+      <c r="H31" s="8">
+        <v>4</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="J31" s="8">
+        <f t="shared" si="15"/>
+        <v>51.94</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8">
+        <v>8.76</v>
+      </c>
+      <c r="G32" s="8">
+        <v>28.04</v>
+      </c>
+      <c r="H32" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="I32" s="8">
+        <f t="shared" si="14"/>
+        <v>1.87</v>
+      </c>
+      <c r="J32" s="8">
+        <f t="shared" si="15"/>
+        <v>52.434800000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8">
+        <v>9.66</v>
+      </c>
+      <c r="G33" s="8">
+        <v>24.94</v>
+      </c>
+      <c r="H33" s="8">
+        <v>4.13</v>
+      </c>
+      <c r="I33" s="8">
+        <f t="shared" si="14"/>
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="J33" s="8">
+        <f t="shared" si="15"/>
+        <v>51.501100000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8">
+        <v>7.98</v>
+      </c>
+      <c r="G34" s="8">
+        <v>23.26</v>
+      </c>
+      <c r="H34" s="8">
+        <v>3.62</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="14"/>
+        <v>1.81</v>
+      </c>
+      <c r="J34" s="8">
+        <f t="shared" si="15"/>
+        <v>42.100600000000007</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8">
+        <v>7.86</v>
+      </c>
+      <c r="G35" s="8">
+        <v>21.97</v>
+      </c>
+      <c r="H35" s="8">
+        <v>4</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="J35" s="8">
+        <f t="shared" si="15"/>
+        <v>43.94</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="G36" s="8">
+        <v>24.42</v>
+      </c>
+      <c r="H36" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="14"/>
+        <v>1.87</v>
+      </c>
+      <c r="J36" s="8">
+        <f t="shared" si="15"/>
+        <v>45.665400000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="11">
+        <f>AVERAGE(F29:F36)</f>
+        <v>8.8237500000000004</v>
+      </c>
+      <c r="G37" s="11">
+        <f t="shared" ref="G37" si="16">AVERAGE(G29:G36)</f>
+        <v>25.083749999999995</v>
+      </c>
+      <c r="H37" s="11">
+        <f t="shared" ref="H37" si="17">AVERAGE(H29:H36)</f>
+        <v>3.8712499999999999</v>
+      </c>
+      <c r="I37" s="11">
+        <f t="shared" ref="I37" si="18">AVERAGE(I29:I36)</f>
+        <v>1.9356249999999999</v>
+      </c>
+      <c r="J37" s="11">
+        <f t="shared" ref="J37" si="19">AVERAGE(J29:J36)</f>
+        <v>48.547449999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="13.8">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="12">
+        <f>STDEV(F29:F36)</f>
+        <v>0.70643850202466796</v>
+      </c>
+      <c r="G38" s="12">
+        <f t="shared" ref="G38:J38" si="20">STDEV(G29:G36)</f>
+        <v>1.8909025622701976</v>
+      </c>
+      <c r="H38" s="12">
+        <f t="shared" si="20"/>
+        <v>0.18185060587510513</v>
+      </c>
+      <c r="I38" s="12">
+        <f t="shared" si="20"/>
+        <v>9.0925302937552563E-2</v>
+      </c>
+      <c r="J38" s="12">
+        <f t="shared" si="20"/>
+        <v>4.2100637090530713</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="E39" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="15">
+        <f>F38/F37</f>
+        <v>8.0061028703744777E-2</v>
+      </c>
+      <c r="G39" s="15">
+        <f t="shared" ref="G39" si="21">G38/G37</f>
+        <v>7.5383567539550431E-2</v>
+      </c>
+      <c r="H39" s="15">
+        <f t="shared" ref="H39" si="22">H38/H37</f>
+        <v>4.6974647949655828E-2</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" ref="I39" si="23">I38/I37</f>
+        <v>4.6974647949655828E-2</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" ref="J39" si="24">J38/J37</f>
+        <v>8.6720594162063541E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="13.8">
+      <c r="B40" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="8">
+        <v>30</v>
+      </c>
+      <c r="C41" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D41" s="8">
+        <f>B41-C41</f>
+        <v>25.5</v>
+      </c>
+      <c r="E41" s="8">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F41" s="8">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="G41" s="8">
+        <v>27.37</v>
+      </c>
+      <c r="H41" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="I41" s="8">
+        <f>H41/2</f>
+        <v>1.875</v>
+      </c>
+      <c r="J41" s="8">
+        <f>I41*G41</f>
+        <v>51.318750000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8">
+        <v>7.98</v>
+      </c>
+      <c r="G42" s="8">
+        <v>28.42</v>
+      </c>
+      <c r="H42" s="8">
+        <v>3.36</v>
+      </c>
+      <c r="I42" s="8">
+        <f t="shared" ref="I42:I48" si="25">H42/2</f>
+        <v>1.68</v>
+      </c>
+      <c r="J42" s="8">
+        <f t="shared" ref="J42:J48" si="26">I42*G42</f>
+        <v>47.745600000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8">
+        <v>6.31</v>
+      </c>
+      <c r="G43" s="8">
+        <v>23.26</v>
+      </c>
+      <c r="H43" s="8">
+        <v>3.23</v>
+      </c>
+      <c r="I43" s="8">
+        <f>H43/2</f>
+        <v>1.615</v>
+      </c>
+      <c r="J43" s="8">
+        <f t="shared" si="26"/>
+        <v>37.564900000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8">
+        <v>7.21</v>
+      </c>
+      <c r="G44" s="8">
+        <v>25.07</v>
+      </c>
+      <c r="H44" s="8">
+        <v>2.97</v>
+      </c>
+      <c r="I44" s="8">
+        <f t="shared" si="25"/>
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="J44" s="8">
+        <f t="shared" si="26"/>
+        <v>37.228950000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8">
+        <v>7.08</v>
+      </c>
+      <c r="G45" s="8">
+        <v>22.1</v>
+      </c>
+      <c r="H45" s="8">
+        <v>3.36</v>
+      </c>
+      <c r="I45" s="8">
+        <f t="shared" si="25"/>
+        <v>1.68</v>
+      </c>
+      <c r="J45" s="8">
+        <f t="shared" si="26"/>
+        <v>37.128</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="11">
+        <f>AVERAGE(F41:F45)</f>
+        <v>7.3900000000000006</v>
+      </c>
+      <c r="G46" s="11">
+        <f t="shared" ref="G46:J46" si="27">AVERAGE(G41:G45)</f>
+        <v>25.244</v>
+      </c>
+      <c r="H46" s="11">
+        <f t="shared" si="27"/>
+        <v>3.3340000000000005</v>
+      </c>
+      <c r="I46" s="11">
+        <f t="shared" si="27"/>
+        <v>1.6670000000000003</v>
+      </c>
+      <c r="J46" s="11">
+        <f t="shared" si="27"/>
+        <v>42.197240000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="13.8">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="12">
+        <f>STDEV(F41:F45)</f>
+        <v>0.80675275022772619</v>
+      </c>
+      <c r="G47" s="12">
+        <f t="shared" ref="G47:J47" si="28">STDEV(G41:G45)</f>
+        <v>2.6673076313016466</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="28"/>
+        <v>0.28183328405282432</v>
+      </c>
+      <c r="I47" s="12">
+        <f t="shared" si="28"/>
+        <v>0.14091664202641216</v>
+      </c>
+      <c r="J47" s="12">
+        <f t="shared" si="28"/>
+        <v>6.8158990042950354</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="15">
+        <f>F47/F46</f>
+        <v>0.10916816647195211</v>
+      </c>
+      <c r="G48" s="15">
+        <f t="shared" ref="G48:J48" si="29">G47/G46</f>
+        <v>0.10566105337116331</v>
+      </c>
+      <c r="H48" s="15">
+        <f t="shared" si="29"/>
+        <v>8.4533078600127251E-2</v>
+      </c>
+      <c r="I48" s="15">
+        <f t="shared" si="29"/>
+        <v>8.4533078600127251E-2</v>
+      </c>
+      <c r="J48" s="15">
+        <f t="shared" si="29"/>
+        <v>0.16152475859309839</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="13.8">
+      <c r="B49" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="B50" s="8">
+        <v>25</v>
+      </c>
+      <c r="C50" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D50" s="8">
+        <f>B50-C50</f>
+        <v>20.5</v>
+      </c>
+      <c r="E50" s="8">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F50" s="8">
+        <v>4.76</v>
+      </c>
+      <c r="G50" s="8">
+        <v>24.03</v>
+      </c>
+      <c r="H50" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="I50" s="8">
+        <f>H50/2</f>
+        <v>1.9350000000000001</v>
+      </c>
+      <c r="J50" s="8">
+        <f>I50*G50</f>
+        <v>46.498050000000006</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="G51" s="8">
+        <v>22.74</v>
+      </c>
+      <c r="H51" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="I51" s="8">
+        <f t="shared" ref="I51:I57" si="30">H51/2</f>
+        <v>1.9350000000000001</v>
+      </c>
+      <c r="J51" s="8">
+        <f t="shared" ref="J51:J57" si="31">I51*G51</f>
+        <v>44.001899999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8">
+        <v>7.34</v>
+      </c>
+      <c r="G52" s="8">
+        <v>20.81</v>
+      </c>
+      <c r="H52" s="8">
+        <v>30.49</v>
+      </c>
+      <c r="I52" s="8">
+        <f>H52/2</f>
+        <v>15.244999999999999</v>
+      </c>
+      <c r="J52" s="8">
+        <f t="shared" si="31"/>
+        <v>317.24844999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8">
+        <v>7.73</v>
+      </c>
+      <c r="G53" s="8">
+        <v>21.97</v>
+      </c>
+      <c r="H53" s="8">
+        <v>3.62</v>
+      </c>
+      <c r="I53" s="8">
+        <f t="shared" ref="I53:I57" si="32">H53/2</f>
+        <v>1.81</v>
+      </c>
+      <c r="J53" s="8">
+        <f t="shared" si="31"/>
+        <v>39.765700000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8">
+        <v>6.18</v>
+      </c>
+      <c r="G54" s="8">
+        <v>23.52</v>
+      </c>
+      <c r="H54" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="I54" s="8">
+        <f t="shared" si="32"/>
+        <v>1.87</v>
+      </c>
+      <c r="J54" s="8">
+        <f t="shared" si="31"/>
+        <v>43.982399999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="F55" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="G55" s="8">
+        <v>17.71</v>
+      </c>
+      <c r="H55" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I55" s="8">
+        <f t="shared" si="32"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J55" s="8">
+        <f t="shared" si="31"/>
+        <v>9.7405000000000008</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="11">
+        <f>AVERAGE(F50:F55)</f>
+        <v>7.0183333333333344</v>
+      </c>
+      <c r="G56" s="11">
+        <f>AVERAGE(G50:G55)</f>
+        <v>21.796666666666667</v>
+      </c>
+      <c r="H56" s="11">
+        <f>AVERAGE(H50:H55)</f>
+        <v>7.7816666666666663</v>
+      </c>
+      <c r="I56" s="11">
+        <f>AVERAGE(I50:I55)</f>
+        <v>3.8908333333333331</v>
+      </c>
+      <c r="J56" s="11">
+        <f>AVERAGE(J50:J55)</f>
+        <v>83.53949999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="13.8">
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" s="12">
+        <f>STDEV(F50:F55)</f>
+        <v>1.3376459421934654</v>
+      </c>
+      <c r="G57" s="12">
+        <f>STDEV(G50:G55)</f>
+        <v>2.3044276223536868</v>
+      </c>
+      <c r="H57" s="12">
+        <f>STDEV(H50:H55)</f>
+        <v>11.176492144974052</v>
+      </c>
+      <c r="I57" s="12">
+        <f>STDEV(I50:I55)</f>
+        <v>5.588246072487026</v>
+      </c>
+      <c r="J57" s="12">
+        <f>STDEV(J50:J55)</f>
+        <v>115.31033454969679</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="E58" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" s="15">
+        <f>F57/F56</f>
+        <v>0.190593105038252</v>
+      </c>
+      <c r="G58" s="15">
+        <f t="shared" ref="G58" si="33">G57/G56</f>
+        <v>0.10572385482583056</v>
+      </c>
+      <c r="H58" s="15">
+        <f t="shared" ref="H58" si="34">H57/H56</f>
+        <v>1.4362594317807735</v>
+      </c>
+      <c r="I58" s="15">
+        <f t="shared" ref="I58" si="35">I57/I56</f>
+        <v>1.4362594317807735</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" ref="J58" si="36">J57/J56</f>
+        <v>1.3803091298092136</v>
       </c>
     </row>
   </sheetData>
@@ -1130,30 +2385,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="B1:J8"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.8">
-      <c r="B1" t="s">
+    <row r="1" spans="2:10" ht="13.8">
+      <c r="B1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>1</v>
-      </c>
+      <c r="G1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10">
       <c r="B2" s="7">
         <v>50</v>
       </c>
@@ -1161,88 +2425,152 @@
         <v>10.199999999999999</v>
       </c>
       <c r="D2" s="7">
-        <f t="shared" ref="D2:D6" si="0">B2-C2</f>
+        <f>B2-C2</f>
         <v>39.799999999999997</v>
       </c>
       <c r="E2" s="7">
         <f>Оборудование!$I$2</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7">
-        <v>45</v>
-      </c>
-      <c r="C3" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8">
+        <f>H2/2</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="8">
+        <f>I2*G2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8">
+        <f t="shared" ref="I3:I5" si="0">H3/2</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="8">
+        <f t="shared" ref="J3:J5" si="1">I3*G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8">
         <f t="shared" si="0"/>
-        <v>34.799999999999997</v>
-      </c>
-      <c r="E3" s="7">
-        <f>Оборудование!$I$2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7">
-        <v>40</v>
-      </c>
-      <c r="C4" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D4" s="7">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8">
         <f t="shared" si="0"/>
-        <v>29.8</v>
-      </c>
-      <c r="E4" s="7">
-        <f>Оборудование!$I$2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7">
-        <v>35</v>
-      </c>
-      <c r="C5" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D5" s="7">
-        <f t="shared" si="0"/>
-        <v>24.8</v>
-      </c>
-      <c r="E5" s="7">
-        <f>Оборудование!$I$2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <v>30</v>
-      </c>
-      <c r="C6" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D6" s="7">
-        <f t="shared" si="0"/>
-        <v>19.8</v>
-      </c>
-      <c r="E6" s="7">
-        <f>Оборудование!$I$2</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="11" t="e">
+        <f>AVERAGE(F2:F5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G6" s="11" t="e">
+        <f t="shared" ref="G6:J6" si="2">AVERAGE(G2:G5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H6" s="11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I6" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="13.8">
+      <c r="E7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="12" t="e">
+        <f>STDEV(F2:F5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="12" t="e">
+        <f t="shared" ref="G7:J7" si="3">STDEV(G2:G5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H7" s="12" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" s="12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="E8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="16" t="e">
+        <f>F7/F6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="16" t="e">
+        <f>G7/G6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H8" s="16" t="e">
+        <f>H7/H6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I8" s="16" t="e">
+        <f>I7/I6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J8" s="16" t="e">
+        <f>J7/J6</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>

--- a/Exams/Semester 2/Physics/VPV/Data.xlsx
+++ b/Exams/Semester 2/Physics/VPV/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mihso\Documents\Study-data\Exams\Semester 2\Physics\VPV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C04A9B-08D9-491B-BE0D-0D53EC65FEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59050C46-DBCF-430D-9910-C6D3868EB8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -863,7 +863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
@@ -1960,11 +1960,11 @@
         <v>3.36</v>
       </c>
       <c r="I42" s="8">
-        <f t="shared" ref="I42:I48" si="25">H42/2</f>
+        <f t="shared" ref="I42:I45" si="25">H42/2</f>
         <v>1.68</v>
       </c>
       <c r="J42" s="8">
-        <f t="shared" ref="J42:J48" si="26">I42*G42</f>
+        <f t="shared" ref="J42:J45" si="26">I42*G42</f>
         <v>47.745600000000003</v>
       </c>
     </row>
@@ -2166,21 +2166,21 @@
         <v>1</v>
       </c>
       <c r="F50" s="8">
-        <v>4.76</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="G50" s="8">
-        <v>24.03</v>
+        <v>23.26</v>
       </c>
       <c r="H50" s="8">
-        <v>3.87</v>
+        <v>3.49</v>
       </c>
       <c r="I50" s="8">
-        <f>H50/2</f>
-        <v>1.9350000000000001</v>
+        <f t="shared" ref="I50" si="30">H50/2</f>
+        <v>1.7450000000000001</v>
       </c>
       <c r="J50" s="8">
         <f>I50*G50</f>
-        <v>46.498050000000006</v>
+        <v>40.588700000000003</v>
       </c>
     </row>
     <row r="51" spans="2:10">
@@ -2189,21 +2189,21 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <v>8.5</v>
+        <v>7.34</v>
       </c>
       <c r="G51" s="8">
-        <v>22.74</v>
+        <v>21.19</v>
       </c>
       <c r="H51" s="8">
-        <v>3.87</v>
+        <v>3.23</v>
       </c>
       <c r="I51" s="8">
-        <f t="shared" ref="I51:I57" si="30">H51/2</f>
-        <v>1.9350000000000001</v>
+        <f>H51/2</f>
+        <v>1.615</v>
       </c>
       <c r="J51" s="8">
-        <f t="shared" ref="J51:J57" si="31">I51*G51</f>
-        <v>44.001899999999999</v>
+        <f>I51*G51</f>
+        <v>34.221850000000003</v>
       </c>
     </row>
     <row r="52" spans="2:10">
@@ -2212,171 +2212,116 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <v>7.34</v>
+        <v>7.73</v>
       </c>
       <c r="G52" s="8">
-        <v>20.81</v>
+        <v>22.1</v>
       </c>
       <c r="H52" s="8">
-        <v>30.49</v>
+        <v>3.62</v>
       </c>
       <c r="I52" s="8">
         <f>H52/2</f>
-        <v>15.244999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="J52" s="8">
-        <f t="shared" si="31"/>
-        <v>317.24844999999999</v>
+        <f>I52*G52</f>
+        <v>40.001000000000005</v>
       </c>
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8">
-        <v>7.73</v>
-      </c>
-      <c r="G53" s="8">
-        <v>21.97</v>
-      </c>
-      <c r="H53" s="8">
-        <v>3.62</v>
-      </c>
-      <c r="I53" s="8">
-        <f t="shared" ref="I53:I57" si="32">H53/2</f>
-        <v>1.81</v>
-      </c>
-      <c r="J53" s="8">
-        <f t="shared" si="31"/>
-        <v>39.765700000000002</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10">
+      <c r="E53" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="11">
+        <f>AVERAGE(F50:F52)</f>
+        <v>7.8133333333333326</v>
+      </c>
+      <c r="G53" s="11">
+        <f>AVERAGE(G50:G52)</f>
+        <v>22.183333333333337</v>
+      </c>
+      <c r="H53" s="11">
+        <f>AVERAGE(H50:H52)</f>
+        <v>3.4466666666666668</v>
+      </c>
+      <c r="I53" s="11">
+        <f>AVERAGE(I50:I52)</f>
+        <v>1.7233333333333334</v>
+      </c>
+      <c r="J53" s="11">
+        <f>AVERAGE(J50:J52)</f>
+        <v>38.270516666666673</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="13.8">
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8">
-        <v>6.18</v>
-      </c>
-      <c r="G54" s="8">
-        <v>23.52</v>
-      </c>
-      <c r="H54" s="8">
-        <v>3.74</v>
-      </c>
-      <c r="I54" s="8">
-        <f t="shared" si="32"/>
-        <v>1.87</v>
-      </c>
-      <c r="J54" s="8">
-        <f t="shared" si="31"/>
-        <v>43.982399999999998</v>
+      <c r="E54" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="12">
+        <f>STDEV(F50:F52)</f>
+        <v>0.52003205029433808</v>
+      </c>
+      <c r="G54" s="12">
+        <f>STDEV(G50:G52)</f>
+        <v>1.0375130521267353</v>
+      </c>
+      <c r="H54" s="12">
+        <f>STDEV(H50:H52)</f>
+        <v>0.19857828011475315</v>
+      </c>
+      <c r="I54" s="12">
+        <f>STDEV(I50:I52)</f>
+        <v>9.9289140057376574E-2</v>
+      </c>
+      <c r="J54" s="12">
+        <f>STDEV(J50:J52)</f>
+        <v>3.5185400602854213</v>
       </c>
     </row>
     <row r="55" spans="2:10">
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
-      <c r="F55" s="8">
-        <v>7.6</v>
-      </c>
-      <c r="G55" s="8">
-        <v>17.71</v>
-      </c>
-      <c r="H55" s="8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I55" s="8">
-        <f t="shared" si="32"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J55" s="8">
+      <c r="E55" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="15">
+        <f>F54/F53</f>
+        <v>6.6557003024019387E-2</v>
+      </c>
+      <c r="G55" s="15">
+        <f t="shared" ref="G55:J55" si="31">G54/G53</f>
+        <v>4.6769934731483172E-2</v>
+      </c>
+      <c r="H55" s="15">
         <f t="shared" si="31"/>
-        <v>9.7405000000000008</v>
+        <v>5.7614588041030895E-2</v>
+      </c>
+      <c r="I55" s="15">
+        <f t="shared" si="31"/>
+        <v>5.7614588041030895E-2</v>
+      </c>
+      <c r="J55" s="15">
+        <f t="shared" si="31"/>
+        <v>9.1938661056803622E-2</v>
       </c>
     </row>
     <row r="56" spans="2:10">
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
-      <c r="E56" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F56" s="11">
-        <f>AVERAGE(F50:F55)</f>
-        <v>7.0183333333333344</v>
-      </c>
-      <c r="G56" s="11">
-        <f>AVERAGE(G50:G55)</f>
-        <v>21.796666666666667</v>
-      </c>
-      <c r="H56" s="11">
-        <f>AVERAGE(H50:H55)</f>
-        <v>7.7816666666666663</v>
-      </c>
-      <c r="I56" s="11">
-        <f>AVERAGE(I50:I55)</f>
-        <v>3.8908333333333331</v>
-      </c>
-      <c r="J56" s="11">
-        <f>AVERAGE(J50:J55)</f>
-        <v>83.53949999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="13.8">
+    </row>
+    <row r="57" spans="2:10">
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
-      <c r="E57" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F57" s="12">
-        <f>STDEV(F50:F55)</f>
-        <v>1.3376459421934654</v>
-      </c>
-      <c r="G57" s="12">
-        <f>STDEV(G50:G55)</f>
-        <v>2.3044276223536868</v>
-      </c>
-      <c r="H57" s="12">
-        <f>STDEV(H50:H55)</f>
-        <v>11.176492144974052</v>
-      </c>
-      <c r="I57" s="12">
-        <f>STDEV(I50:I55)</f>
-        <v>5.588246072487026</v>
-      </c>
-      <c r="J57" s="12">
-        <f>STDEV(J50:J55)</f>
-        <v>115.31033454969679</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="E58" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F58" s="15">
-        <f>F57/F56</f>
-        <v>0.190593105038252</v>
-      </c>
-      <c r="G58" s="15">
-        <f t="shared" ref="G58" si="33">G57/G56</f>
-        <v>0.10572385482583056</v>
-      </c>
-      <c r="H58" s="15">
-        <f t="shared" ref="H58" si="34">H57/H56</f>
-        <v>1.4362594317807735</v>
-      </c>
-      <c r="I58" s="15">
-        <f t="shared" ref="I58" si="35">I57/I56</f>
-        <v>1.4362594317807735</v>
-      </c>
-      <c r="J58" s="15">
-        <f t="shared" ref="J58" si="36">J57/J56</f>
-        <v>1.3803091298092136</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2385,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:J8"/>
+  <dimension ref="B1:J12"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="2:10" ht="13.8">
@@ -2432,16 +2377,22 @@
         <f>Оборудование!$I$2</f>
         <v>1</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="F2" s="8">
+        <v>9.83</v>
+      </c>
+      <c r="G2" s="8">
+        <v>23.84</v>
+      </c>
+      <c r="H2" s="8">
+        <v>4.79</v>
+      </c>
       <c r="I2" s="8">
         <f>H2/2</f>
-        <v>0</v>
+        <v>2.395</v>
       </c>
       <c r="J2" s="8">
         <f>I2*G2</f>
-        <v>0</v>
+        <v>57.096800000000002</v>
       </c>
     </row>
     <row r="3" spans="2:10">
@@ -2449,16 +2400,22 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="F3" s="8">
+        <v>12.14</v>
+      </c>
+      <c r="G3" s="8">
+        <v>27.39</v>
+      </c>
+      <c r="H3" s="8">
+        <v>4.79</v>
+      </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I5" si="0">H3/2</f>
-        <v>0</v>
+        <f t="shared" ref="I3:I7" si="0">H3/2</f>
+        <v>2.395</v>
       </c>
       <c r="J3" s="8">
-        <f t="shared" ref="J3:J5" si="1">I3*G3</f>
-        <v>0</v>
+        <f t="shared" ref="J3:J7" si="1">I3*G3</f>
+        <v>65.599050000000005</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -2466,16 +2423,22 @@
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="F4" s="8">
+        <v>9.83</v>
+      </c>
+      <c r="G4" s="8">
+        <v>31.87</v>
+      </c>
+      <c r="H4" s="8">
+        <v>4.63</v>
+      </c>
       <c r="I4" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.3149999999999999</v>
       </c>
       <c r="J4" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>73.779049999999998</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -2483,94 +2446,138 @@
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="F5" s="8">
+        <v>11.68</v>
+      </c>
+      <c r="G5" s="8">
+        <v>28.32</v>
+      </c>
+      <c r="H5" s="8">
+        <v>4.4800000000000004</v>
+      </c>
       <c r="I5" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="J5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>63.436800000000005</v>
       </c>
     </row>
     <row r="6" spans="2:10">
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="8">
+        <v>12.61</v>
+      </c>
+      <c r="G6" s="8">
+        <v>28.01</v>
+      </c>
+      <c r="H6" s="8">
+        <v>4.79</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="0"/>
+        <v>2.395</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" si="1"/>
+        <v>67.083950000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="F7" s="8">
+        <v>11.83</v>
+      </c>
+      <c r="G7" s="8">
+        <v>31.41</v>
+      </c>
+      <c r="H7" s="8">
+        <v>4.79</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>2.395</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="1"/>
+        <v>75.226950000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="E10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="11" t="e">
-        <f>AVERAGE(F2:F5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="11" t="e">
-        <f t="shared" ref="G6:J6" si="2">AVERAGE(G2:G5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H6" s="11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I6" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="13.8">
-      <c r="E7" s="13" t="s">
+      <c r="F10" s="11">
+        <f>AVERAGE(F2:F7)</f>
+        <v>11.32</v>
+      </c>
+      <c r="G10" s="11">
+        <f>AVERAGE(G2:G7)</f>
+        <v>28.473333333333333</v>
+      </c>
+      <c r="H10" s="11">
+        <f>AVERAGE(H2:H7)</f>
+        <v>4.7116666666666669</v>
+      </c>
+      <c r="I10" s="11">
+        <f>AVERAGE(I2:I7)</f>
+        <v>2.3558333333333334</v>
+      </c>
+      <c r="J10" s="11">
+        <f>AVERAGE(J2:J7)</f>
+        <v>67.037099999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="13.8">
+      <c r="E11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="12" t="e">
-        <f>STDEV(F2:F5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G7" s="12" t="e">
-        <f t="shared" ref="G7:J7" si="3">STDEV(G2:G5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H7" s="12" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I7" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="E8" s="14" t="s">
+      <c r="F11" s="12">
+        <f>STDEV(F2:F7)</f>
+        <v>1.1971967256888068</v>
+      </c>
+      <c r="G11" s="12">
+        <f>STDEV(G2:G7)</f>
+        <v>2.9339711427801514</v>
+      </c>
+      <c r="H11" s="12">
+        <f>STDEV(H2:H7)</f>
+        <v>0.13029453813060099</v>
+      </c>
+      <c r="I11" s="12">
+        <f>STDEV(I2:I7)</f>
+        <v>6.5147269065300495E-2</v>
+      </c>
+      <c r="J11" s="12">
+        <f>STDEV(J2:J7)</f>
+        <v>6.7285873663050539</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="E12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="16" t="e">
-        <f>F7/F6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G8" s="16" t="e">
-        <f>G7/G6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H8" s="16" t="e">
-        <f>H7/H6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="16" t="e">
-        <f>I7/I6</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J8" s="16" t="e">
-        <f>J7/J6</f>
-        <v>#DIV/0!</v>
+      <c r="F12" s="16">
+        <f>F11/F10</f>
+        <v>0.10575942806438222</v>
+      </c>
+      <c r="G12" s="16">
+        <f>G11/G10</f>
+        <v>0.1030427701749058</v>
+      </c>
+      <c r="H12" s="16">
+        <f>H11/H10</f>
+        <v>2.7653598471298405E-2</v>
+      </c>
+      <c r="I12" s="16">
+        <f>I11/I10</f>
+        <v>2.7653598471298405E-2</v>
+      </c>
+      <c r="J12" s="16">
+        <f>J11/J10</f>
+        <v>0.10037109848583925</v>
       </c>
     </row>
   </sheetData>

--- a/Exams/Semester 2/Physics/VPV/Data.xlsx
+++ b/Exams/Semester 2/Physics/VPV/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mihso\Documents\Study-data\Exams\Semester 2\Physics\VPV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59050C46-DBCF-430D-9910-C6D3868EB8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9DF82A-4314-4D02-85EA-A5EC3C1C9342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Оборудование" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="22">
   <si>
     <t>Радиус капли</t>
   </si>
@@ -1928,21 +1928,21 @@
         <v>1</v>
       </c>
       <c r="F41" s="8">
-        <v>8.3699999999999992</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="G41" s="8">
-        <v>27.37</v>
+        <v>30</v>
       </c>
       <c r="H41" s="8">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="I41" s="8">
         <f>H41/2</f>
-        <v>1.875</v>
+        <v>1.63</v>
       </c>
       <c r="J41" s="8">
         <f>I41*G41</f>
-        <v>51.318750000000001</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="42" spans="2:10">
@@ -1951,377 +1951,399 @@
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8">
-        <v>7.98</v>
+        <v>8.58</v>
       </c>
       <c r="G42" s="8">
-        <v>28.42</v>
+        <v>28.95</v>
       </c>
       <c r="H42" s="8">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="I42" s="8">
-        <f t="shared" ref="I42:I45" si="25">H42/2</f>
-        <v>1.68</v>
+        <f t="shared" ref="I42:I46" si="25">H42/2</f>
+        <v>1.5649999999999999</v>
       </c>
       <c r="J42" s="8">
-        <f t="shared" ref="J42:J45" si="26">I42*G42</f>
-        <v>47.745600000000003</v>
+        <f t="shared" ref="J42:J46" si="26">I42*G42</f>
+        <v>45.306749999999994</v>
       </c>
     </row>
     <row r="43" spans="2:10">
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8">
-        <v>6.31</v>
-      </c>
-      <c r="G43" s="8">
-        <v>23.26</v>
-      </c>
-      <c r="H43" s="8">
-        <v>3.23</v>
-      </c>
-      <c r="I43" s="8">
-        <f>H43/2</f>
-        <v>1.615</v>
-      </c>
-      <c r="J43" s="8">
-        <f t="shared" si="26"/>
-        <v>37.564900000000002</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10">
+      <c r="E43" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="11">
+        <f>AVERAGE(F41:F42)</f>
+        <v>8.5150000000000006</v>
+      </c>
+      <c r="G43" s="11">
+        <f t="shared" ref="G43:J43" si="27">AVERAGE(G41:G42)</f>
+        <v>29.475000000000001</v>
+      </c>
+      <c r="H43" s="11">
+        <f t="shared" si="27"/>
+        <v>3.1949999999999998</v>
+      </c>
+      <c r="I43" s="11">
+        <f t="shared" si="27"/>
+        <v>1.5974999999999999</v>
+      </c>
+      <c r="J43" s="11">
+        <f t="shared" si="27"/>
+        <v>47.103375</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="13.8">
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8">
-        <v>7.21</v>
-      </c>
-      <c r="G44" s="8">
-        <v>25.07</v>
-      </c>
-      <c r="H44" s="8">
-        <v>2.97</v>
-      </c>
-      <c r="I44" s="8">
-        <f t="shared" si="25"/>
-        <v>1.4850000000000001</v>
-      </c>
-      <c r="J44" s="8">
-        <f t="shared" si="26"/>
-        <v>37.228950000000005</v>
+      <c r="E44" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="12">
+        <f>STDEV(F41:F42)</f>
+        <v>9.1923881554251727E-2</v>
+      </c>
+      <c r="G44" s="12">
+        <f t="shared" ref="G44:J44" si="28">STDEV(G41:G42)</f>
+        <v>0.74246212024587532</v>
+      </c>
+      <c r="H44" s="12">
+        <f t="shared" si="28"/>
+        <v>9.1923881554251102E-2</v>
+      </c>
+      <c r="I44" s="12">
+        <f t="shared" si="28"/>
+        <v>4.5961940777125551E-2</v>
+      </c>
+      <c r="J44" s="12">
+        <f t="shared" si="28"/>
+        <v>2.5408114414985654</v>
       </c>
     </row>
     <row r="45" spans="2:10">
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8">
-        <v>7.08</v>
-      </c>
-      <c r="G45" s="8">
-        <v>22.1</v>
-      </c>
-      <c r="H45" s="8">
-        <v>3.36</v>
-      </c>
-      <c r="I45" s="8">
-        <f t="shared" si="25"/>
-        <v>1.68</v>
-      </c>
-      <c r="J45" s="8">
-        <f t="shared" si="26"/>
-        <v>37.128</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10">
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="11">
-        <f>AVERAGE(F41:F45)</f>
-        <v>7.3900000000000006</v>
-      </c>
-      <c r="G46" s="11">
-        <f t="shared" ref="G46:J46" si="27">AVERAGE(G41:G45)</f>
-        <v>25.244</v>
-      </c>
-      <c r="H46" s="11">
-        <f t="shared" si="27"/>
-        <v>3.3340000000000005</v>
-      </c>
-      <c r="I46" s="11">
-        <f t="shared" si="27"/>
-        <v>1.6670000000000003</v>
-      </c>
-      <c r="J46" s="11">
-        <f t="shared" si="27"/>
-        <v>42.197240000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="13.8">
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F47" s="12">
-        <f>STDEV(F41:F45)</f>
-        <v>0.80675275022772619</v>
-      </c>
-      <c r="G47" s="12">
-        <f t="shared" ref="G47:J47" si="28">STDEV(G41:G45)</f>
-        <v>2.6673076313016466</v>
-      </c>
-      <c r="H47" s="12">
-        <f t="shared" si="28"/>
-        <v>0.28183328405282432</v>
-      </c>
-      <c r="I47" s="12">
-        <f t="shared" si="28"/>
-        <v>0.14091664202641216</v>
-      </c>
-      <c r="J47" s="12">
-        <f t="shared" si="28"/>
-        <v>6.8158990042950354</v>
+      <c r="E45" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" s="15">
+        <f>F44/F43</f>
+        <v>1.0795523376893918E-2</v>
+      </c>
+      <c r="G45" s="15">
+        <f t="shared" ref="G45:J45" si="29">G44/G43</f>
+        <v>2.5189554546085676E-2</v>
+      </c>
+      <c r="H45" s="15">
+        <f t="shared" si="29"/>
+        <v>2.8771167935602849E-2</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="29"/>
+        <v>2.8771167935602849E-2</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="29"/>
+        <v>5.3941176009119629E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="13.8">
+      <c r="B46" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="8">
+        <v>25</v>
+      </c>
+      <c r="C47" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D47" s="8">
+        <f>B47-C47</f>
+        <v>20.5</v>
+      </c>
+      <c r="E47" s="8">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F47" s="8">
+        <v>8.58</v>
+      </c>
+      <c r="G47" s="8">
+        <v>21.79</v>
+      </c>
+      <c r="H47" s="8">
+        <v>3.39</v>
+      </c>
+      <c r="I47" s="8">
+        <f t="shared" ref="I47" si="30">H47/2</f>
+        <v>1.6950000000000001</v>
+      </c>
+      <c r="J47" s="8">
+        <f>I47*G47</f>
+        <v>36.934049999999999</v>
       </c>
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="8"/>
+      <c r="F48" s="8">
+        <v>8.84</v>
+      </c>
+      <c r="G48" s="8">
         <v>21</v>
       </c>
-      <c r="F48" s="15">
-        <f>F47/F46</f>
-        <v>0.10916816647195211</v>
-      </c>
-      <c r="G48" s="15">
-        <f t="shared" ref="G48:J48" si="29">G47/G46</f>
-        <v>0.10566105337116331</v>
-      </c>
-      <c r="H48" s="15">
-        <f t="shared" si="29"/>
-        <v>8.4533078600127251E-2</v>
-      </c>
-      <c r="I48" s="15">
-        <f t="shared" si="29"/>
-        <v>8.4533078600127251E-2</v>
-      </c>
-      <c r="J48" s="15">
-        <f t="shared" si="29"/>
-        <v>0.16152475859309839</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" ht="13.8">
-      <c r="B49" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="18" t="s">
-        <v>18</v>
+      <c r="H48" s="8">
+        <v>3.26</v>
+      </c>
+      <c r="I48" s="8">
+        <f>H48/2</f>
+        <v>1.63</v>
+      </c>
+      <c r="J48" s="8">
+        <f>I48*G48</f>
+        <v>34.229999999999997</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8">
+        <v>8.32</v>
+      </c>
+      <c r="G49" s="8">
+        <v>22.31</v>
+      </c>
+      <c r="H49" s="8">
+        <v>3.78</v>
+      </c>
+      <c r="I49" s="8">
+        <f>H49/2</f>
+        <v>1.89</v>
+      </c>
+      <c r="J49" s="8">
+        <f>I49*G49</f>
+        <v>42.165899999999993</v>
       </c>
     </row>
     <row r="50" spans="2:10">
-      <c r="B50" s="8">
-        <v>25</v>
-      </c>
-      <c r="C50" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="D50" s="8">
-        <f>B50-C50</f>
-        <v>20.5</v>
-      </c>
-      <c r="E50" s="8">
-        <f>Оборудование!$I$2</f>
-        <v>1</v>
-      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
       <c r="F50" s="8">
-        <v>8.3699999999999992</v>
+        <v>7.93</v>
       </c>
       <c r="G50" s="8">
-        <v>23.26</v>
+        <v>19.57</v>
       </c>
       <c r="H50" s="8">
-        <v>3.49</v>
+        <v>3.13</v>
       </c>
       <c r="I50" s="8">
-        <f t="shared" ref="I50" si="30">H50/2</f>
-        <v>1.7450000000000001</v>
+        <f t="shared" ref="I50:I57" si="31">H50/2</f>
+        <v>1.5649999999999999</v>
       </c>
       <c r="J50" s="8">
-        <f>I50*G50</f>
-        <v>40.588700000000003</v>
+        <f t="shared" ref="J50:J57" si="32">I50*G50</f>
+        <v>30.627050000000001</v>
       </c>
     </row>
     <row r="51" spans="2:10">
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
       <c r="F51" s="8">
-        <v>7.34</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="G51" s="8">
-        <v>21.19</v>
+        <v>21.13</v>
       </c>
       <c r="H51" s="8">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="I51" s="8">
-        <f>H51/2</f>
-        <v>1.615</v>
+        <f t="shared" si="31"/>
+        <v>1.63</v>
       </c>
       <c r="J51" s="8">
-        <f>I51*G51</f>
-        <v>34.221850000000003</v>
+        <f t="shared" si="32"/>
+        <v>34.441899999999997</v>
       </c>
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
       <c r="F52" s="8">
-        <v>7.73</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="G52" s="8">
-        <v>22.1</v>
+        <v>24</v>
       </c>
       <c r="H52" s="8">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="I52" s="8">
-        <f>H52/2</f>
-        <v>1.81</v>
+        <f t="shared" si="31"/>
+        <v>1.76</v>
       </c>
       <c r="J52" s="8">
-        <f>I52*G52</f>
-        <v>40.001000000000005</v>
+        <f t="shared" si="32"/>
+        <v>42.24</v>
       </c>
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" s="11">
-        <f>AVERAGE(F50:F52)</f>
-        <v>7.8133333333333326</v>
-      </c>
-      <c r="G53" s="11">
-        <f>AVERAGE(G50:G52)</f>
-        <v>22.183333333333337</v>
-      </c>
-      <c r="H53" s="11">
-        <f>AVERAGE(H50:H52)</f>
-        <v>3.4466666666666668</v>
-      </c>
-      <c r="I53" s="11">
-        <f>AVERAGE(I50:I52)</f>
-        <v>1.7233333333333334</v>
-      </c>
-      <c r="J53" s="11">
-        <f>AVERAGE(J50:J52)</f>
-        <v>38.270516666666673</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="13.8">
+      <c r="F53" s="8">
+        <v>7.8</v>
+      </c>
+      <c r="G53" s="8">
+        <v>18.66</v>
+      </c>
+      <c r="H53" s="8">
+        <v>3.39</v>
+      </c>
+      <c r="I53" s="8">
+        <f t="shared" si="31"/>
+        <v>1.6950000000000001</v>
+      </c>
+      <c r="J53" s="8">
+        <f t="shared" si="32"/>
+        <v>31.628700000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="13" t="s">
+      <c r="F54" s="8">
+        <v>7.8</v>
+      </c>
+      <c r="G54" s="8">
+        <v>20.48</v>
+      </c>
+      <c r="H54" s="8">
+        <v>3</v>
+      </c>
+      <c r="I54" s="8">
+        <f t="shared" si="31"/>
+        <v>1.5</v>
+      </c>
+      <c r="J54" s="8">
+        <f t="shared" si="32"/>
+        <v>30.72</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="E55" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="11">
+        <f>AVERAGE(F47:F54)</f>
+        <v>8.2712500000000002</v>
+      </c>
+      <c r="G55" s="11">
+        <f t="shared" ref="G55:J55" si="33">AVERAGE(G47:G54)</f>
+        <v>21.117499999999996</v>
+      </c>
+      <c r="H55" s="11">
+        <f t="shared" si="33"/>
+        <v>3.3412500000000001</v>
+      </c>
+      <c r="I55" s="11">
+        <f t="shared" si="33"/>
+        <v>1.670625</v>
+      </c>
+      <c r="J55" s="11">
+        <f t="shared" si="33"/>
+        <v>35.373450000000005</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="13.8">
+      <c r="E56" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F54" s="12">
-        <f>STDEV(F50:F52)</f>
-        <v>0.52003205029433808</v>
-      </c>
-      <c r="G54" s="12">
-        <f>STDEV(G50:G52)</f>
-        <v>1.0375130521267353</v>
-      </c>
-      <c r="H54" s="12">
-        <f>STDEV(H50:H52)</f>
-        <v>0.19857828011475315</v>
-      </c>
-      <c r="I54" s="12">
-        <f>STDEV(I50:I52)</f>
-        <v>9.9289140057376574E-2</v>
-      </c>
-      <c r="J54" s="12">
-        <f>STDEV(J50:J52)</f>
-        <v>3.5185400602854213</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="14" t="s">
+      <c r="F56" s="12">
+        <f>STDEV(F47:F54)</f>
+        <v>0.38650217149639476</v>
+      </c>
+      <c r="G56" s="12">
+        <f t="shared" ref="G56:J56" si="34">STDEV(G47:G54)</f>
+        <v>1.6491361374974471</v>
+      </c>
+      <c r="H56" s="12">
+        <f t="shared" si="34"/>
+        <v>0.24008555022860378</v>
+      </c>
+      <c r="I56" s="12">
+        <f t="shared" si="34"/>
+        <v>0.12004277511430189</v>
+      </c>
+      <c r="J56" s="12">
+        <f t="shared" si="34"/>
+        <v>4.7223433044410674</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="E57" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F55" s="15">
-        <f>F54/F53</f>
-        <v>6.6557003024019387E-2</v>
-      </c>
-      <c r="G55" s="15">
-        <f t="shared" ref="G55:J55" si="31">G54/G53</f>
-        <v>4.6769934731483172E-2</v>
-      </c>
-      <c r="H55" s="15">
-        <f t="shared" si="31"/>
-        <v>5.7614588041030895E-2</v>
-      </c>
-      <c r="I55" s="15">
-        <f t="shared" si="31"/>
-        <v>5.7614588041030895E-2</v>
-      </c>
-      <c r="J55" s="15">
-        <f t="shared" si="31"/>
-        <v>9.1938661056803622E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
+      <c r="F57" s="15">
+        <f>F56/F55</f>
+        <v>4.6728387063188125E-2</v>
+      </c>
+      <c r="G57" s="15">
+        <f t="shared" ref="G57:J57" si="35">G56/G55</f>
+        <v>7.8093341422869542E-2</v>
+      </c>
+      <c r="H57" s="15">
+        <f t="shared" si="35"/>
+        <v>7.1855009421205776E-2</v>
+      </c>
+      <c r="I57" s="15">
+        <f t="shared" si="35"/>
+        <v>7.1855009421205776E-2</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="35"/>
+        <v>0.13349965311387685</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2330,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:J12"/>
+  <dimension ref="B1:J22"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="2:10" ht="13.8">
@@ -2410,11 +2432,11 @@
         <v>4.79</v>
       </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I7" si="0">H3/2</f>
+        <f t="shared" ref="I3:I8" si="0">H3/2</f>
         <v>2.395</v>
       </c>
       <c r="J3" s="8">
-        <f t="shared" ref="J3:J7" si="1">I3*G3</f>
+        <f t="shared" ref="J3:J8" si="1">I3*G3</f>
         <v>65.599050000000005</v>
       </c>
     </row>
@@ -2505,79 +2527,364 @@
         <v>75.226950000000002</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
-      <c r="E10" s="11" t="s">
+    <row r="8" spans="2:10">
+      <c r="F8" s="8">
+        <v>11.68</v>
+      </c>
+      <c r="G8" s="8">
+        <v>28.94</v>
+      </c>
+      <c r="H8" s="8">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J8" s="8">
+        <f t="shared" si="1"/>
+        <v>64.825600000000009</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="E9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="11">
-        <f>AVERAGE(F2:F7)</f>
-        <v>11.32</v>
-      </c>
-      <c r="G10" s="11">
-        <f>AVERAGE(G2:G7)</f>
-        <v>28.473333333333333</v>
-      </c>
-      <c r="H10" s="11">
-        <f>AVERAGE(H2:H7)</f>
-        <v>4.7116666666666669</v>
-      </c>
-      <c r="I10" s="11">
-        <f>AVERAGE(I2:I7)</f>
-        <v>2.3558333333333334</v>
-      </c>
-      <c r="J10" s="11">
-        <f>AVERAGE(J2:J7)</f>
-        <v>67.037099999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="13.8">
-      <c r="E11" s="13" t="s">
+      <c r="F9" s="11">
+        <f>AVERAGE(F2:F8)</f>
+        <v>11.37142857142857</v>
+      </c>
+      <c r="G9" s="11">
+        <f t="shared" ref="G9:J9" si="2">AVERAGE(G2:G8)</f>
+        <v>28.54</v>
+      </c>
+      <c r="H9" s="11">
+        <f t="shared" si="2"/>
+        <v>4.6785714285714288</v>
+      </c>
+      <c r="I9" s="11">
+        <f t="shared" si="2"/>
+        <v>2.3392857142857144</v>
+      </c>
+      <c r="J9" s="11">
+        <f t="shared" si="2"/>
+        <v>66.721171428571424</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="13.8">
+      <c r="E10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="12">
-        <f>STDEV(F2:F7)</f>
-        <v>1.1971967256888068</v>
-      </c>
-      <c r="G11" s="12">
-        <f>STDEV(G2:G7)</f>
-        <v>2.9339711427801514</v>
-      </c>
-      <c r="H11" s="12">
-        <f>STDEV(H2:H7)</f>
-        <v>0.13029453813060099</v>
-      </c>
-      <c r="I11" s="12">
-        <f>STDEV(I2:I7)</f>
-        <v>6.5147269065300495E-2</v>
-      </c>
-      <c r="J11" s="12">
-        <f>STDEV(J2:J7)</f>
-        <v>6.7285873663050539</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="E12" s="14" t="s">
+      <c r="F10" s="12">
+        <f>STDEV(F2:F8)</f>
+        <v>1.1013238786634409</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" ref="G10:J10" si="3">STDEV(G2:G8)</f>
+        <v>2.6841385955274371</v>
+      </c>
+      <c r="H10" s="12">
+        <f t="shared" si="3"/>
+        <v>0.14769660021234635</v>
+      </c>
+      <c r="I10" s="12">
+        <f t="shared" si="3"/>
+        <v>7.3848300106173173E-2</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="3"/>
+        <v>6.1989447481578885</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="E11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="16">
-        <f>F11/F10</f>
-        <v>0.10575942806438222</v>
-      </c>
-      <c r="G12" s="16">
-        <f>G11/G10</f>
-        <v>0.1030427701749058</v>
-      </c>
-      <c r="H12" s="16">
-        <f>H11/H10</f>
-        <v>2.7653598471298405E-2</v>
-      </c>
-      <c r="I12" s="16">
-        <f>I11/I10</f>
-        <v>2.7653598471298405E-2</v>
-      </c>
-      <c r="J12" s="16">
-        <f>J11/J10</f>
-        <v>0.10037109848583925</v>
+      <c r="F11" s="16">
+        <f>F10/F9</f>
+        <v>9.6850089832212161E-2</v>
+      </c>
+      <c r="G11" s="16">
+        <f t="shared" ref="G11:J11" si="4">G10/G9</f>
+        <v>9.4048303977835923E-2</v>
+      </c>
+      <c r="H11" s="16">
+        <f t="shared" si="4"/>
+        <v>3.1568738976684711E-2</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="4"/>
+        <v>3.1568738976684711E-2</v>
+      </c>
+      <c r="J11" s="16">
+        <f t="shared" si="4"/>
+        <v>9.2908212122657194E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="13.8">
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="7">
+        <v>45</v>
+      </c>
+      <c r="C13" s="7">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D13" s="7">
+        <f>B13-C13</f>
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E13" s="7">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="8">
+        <v>9.83</v>
+      </c>
+      <c r="G13" s="8">
+        <v>23.84</v>
+      </c>
+      <c r="H13" s="8">
+        <v>4.79</v>
+      </c>
+      <c r="I13" s="8">
+        <f>H13/2</f>
+        <v>2.395</v>
+      </c>
+      <c r="J13" s="8">
+        <f>I13*G13</f>
+        <v>57.096800000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
+        <v>12.14</v>
+      </c>
+      <c r="G14" s="8">
+        <v>27.39</v>
+      </c>
+      <c r="H14" s="8">
+        <v>4.79</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" ref="I14:I19" si="5">H14/2</f>
+        <v>2.395</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" ref="J14:J19" si="6">I14*G14</f>
+        <v>65.599050000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
+        <v>9.83</v>
+      </c>
+      <c r="G15" s="8">
+        <v>31.87</v>
+      </c>
+      <c r="H15" s="8">
+        <v>4.63</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="5"/>
+        <v>2.3149999999999999</v>
+      </c>
+      <c r="J15" s="8">
+        <f t="shared" si="6"/>
+        <v>73.779049999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
+        <v>11.68</v>
+      </c>
+      <c r="G16" s="8">
+        <v>28.32</v>
+      </c>
+      <c r="H16" s="8">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="5"/>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="6"/>
+        <v>63.436800000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="F17" s="8">
+        <v>12.61</v>
+      </c>
+      <c r="G17" s="8">
+        <v>28.01</v>
+      </c>
+      <c r="H17" s="8">
+        <v>4.79</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="5"/>
+        <v>2.395</v>
+      </c>
+      <c r="J17" s="8">
+        <f t="shared" si="6"/>
+        <v>67.083950000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="F18" s="8">
+        <v>11.83</v>
+      </c>
+      <c r="G18" s="8">
+        <v>31.41</v>
+      </c>
+      <c r="H18" s="8">
+        <v>4.79</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="5"/>
+        <v>2.395</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="6"/>
+        <v>75.226950000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="F19" s="8">
+        <v>11.68</v>
+      </c>
+      <c r="G19" s="8">
+        <v>28.94</v>
+      </c>
+      <c r="H19" s="8">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="5"/>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J19" s="8">
+        <f t="shared" si="6"/>
+        <v>64.825600000000009</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="E20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="11">
+        <f>AVERAGE(F13:F19)</f>
+        <v>11.37142857142857</v>
+      </c>
+      <c r="G20" s="11">
+        <f t="shared" ref="G20" si="7">AVERAGE(G13:G19)</f>
+        <v>28.54</v>
+      </c>
+      <c r="H20" s="11">
+        <f t="shared" ref="H20" si="8">AVERAGE(H13:H19)</f>
+        <v>4.6785714285714288</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" ref="I20" si="9">AVERAGE(I13:I19)</f>
+        <v>2.3392857142857144</v>
+      </c>
+      <c r="J20" s="11">
+        <f t="shared" ref="J20" si="10">AVERAGE(J13:J19)</f>
+        <v>66.721171428571424</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="13.8">
+      <c r="E21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="12">
+        <f>STDEV(F13:F19)</f>
+        <v>1.1013238786634409</v>
+      </c>
+      <c r="G21" s="12">
+        <f t="shared" ref="G21:J21" si="11">STDEV(G13:G19)</f>
+        <v>2.6841385955274371</v>
+      </c>
+      <c r="H21" s="12">
+        <f t="shared" si="11"/>
+        <v>0.14769660021234635</v>
+      </c>
+      <c r="I21" s="12">
+        <f t="shared" si="11"/>
+        <v>7.3848300106173173E-2</v>
+      </c>
+      <c r="J21" s="12">
+        <f t="shared" si="11"/>
+        <v>6.1989447481578885</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="E22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="16">
+        <f>F21/F20</f>
+        <v>9.6850089832212161E-2</v>
+      </c>
+      <c r="G22" s="16">
+        <f t="shared" ref="G22" si="12">G21/G20</f>
+        <v>9.4048303977835923E-2</v>
+      </c>
+      <c r="H22" s="16">
+        <f t="shared" ref="H22" si="13">H21/H20</f>
+        <v>3.1568738976684711E-2</v>
+      </c>
+      <c r="I22" s="16">
+        <f t="shared" ref="I22" si="14">I21/I20</f>
+        <v>3.1568738976684711E-2</v>
+      </c>
+      <c r="J22" s="16">
+        <f t="shared" ref="J22" si="15">J21/J20</f>
+        <v>9.2908212122657194E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Exams/Semester 2/Physics/VPV/Data.xlsx
+++ b/Exams/Semester 2/Physics/VPV/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mihso\Documents\Study-data\Exams\Semester 2\Physics\VPV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9DF82A-4314-4D02-85EA-A5EC3C1C9342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00C4003-63AC-45D1-A7FA-E6CCC73B6514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Оборудование" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="22">
   <si>
     <t>Радиус капли</t>
   </si>
@@ -2352,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:J22"/>
+  <dimension ref="B1:J59"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="2:10" ht="13.8">
@@ -2400,21 +2400,21 @@
         <v>1</v>
       </c>
       <c r="F2" s="8">
-        <v>9.83</v>
+        <v>11.37</v>
       </c>
       <c r="G2" s="8">
-        <v>23.84</v>
+        <v>24.92</v>
       </c>
       <c r="H2" s="8">
-        <v>4.79</v>
+        <v>3.4</v>
       </c>
       <c r="I2" s="8">
         <f>H2/2</f>
-        <v>2.395</v>
+        <v>1.7</v>
       </c>
       <c r="J2" s="8">
         <f>I2*G2</f>
-        <v>57.096800000000002</v>
+        <v>42.364000000000004</v>
       </c>
     </row>
     <row r="3" spans="2:10">
@@ -2423,21 +2423,21 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="8">
-        <v>12.14</v>
+        <v>11.99</v>
       </c>
       <c r="G3" s="8">
         <v>27.39</v>
       </c>
       <c r="H3" s="8">
-        <v>4.79</v>
+        <v>4.63</v>
       </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I8" si="0">H3/2</f>
-        <v>2.395</v>
+        <f t="shared" ref="I3:I9" si="0">H3/2</f>
+        <v>2.3149999999999999</v>
       </c>
       <c r="J3" s="8">
-        <f t="shared" ref="J3:J8" si="1">I3*G3</f>
-        <v>65.599050000000005</v>
+        <f t="shared" ref="J3:J9" si="1">I3*G3</f>
+        <v>63.407850000000003</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -2446,21 +2446,21 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="8">
-        <v>9.83</v>
+        <v>12.45</v>
       </c>
       <c r="G4" s="8">
-        <v>31.87</v>
+        <v>29.4</v>
       </c>
       <c r="H4" s="8">
-        <v>4.63</v>
+        <v>4.17</v>
       </c>
       <c r="I4" s="8">
         <f t="shared" si="0"/>
-        <v>2.3149999999999999</v>
+        <v>2.085</v>
       </c>
       <c r="J4" s="8">
         <f t="shared" si="1"/>
-        <v>73.779049999999998</v>
+        <v>61.298999999999999</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -2469,21 +2469,21 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="8">
-        <v>11.68</v>
+        <v>11.83</v>
       </c>
       <c r="G5" s="8">
-        <v>28.32</v>
+        <v>27.39</v>
       </c>
       <c r="H5" s="8">
-        <v>4.4800000000000004</v>
+        <v>4.32</v>
       </c>
       <c r="I5" s="8">
         <f t="shared" si="0"/>
-        <v>2.2400000000000002</v>
+        <v>2.16</v>
       </c>
       <c r="J5" s="8">
         <f t="shared" si="1"/>
-        <v>63.436800000000005</v>
+        <v>59.162400000000005</v>
       </c>
     </row>
     <row r="6" spans="2:10">
@@ -2491,219 +2491,215 @@
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="F6" s="8">
-        <v>12.61</v>
+        <v>12.92</v>
       </c>
       <c r="G6" s="8">
-        <v>28.01</v>
+        <v>33.57</v>
       </c>
       <c r="H6" s="8">
-        <v>4.79</v>
+        <v>4.32</v>
       </c>
       <c r="I6" s="8">
         <f t="shared" si="0"/>
-        <v>2.395</v>
+        <v>2.16</v>
       </c>
       <c r="J6" s="8">
         <f t="shared" si="1"/>
-        <v>67.083950000000002</v>
+        <v>72.511200000000002</v>
       </c>
     </row>
     <row r="7" spans="2:10">
       <c r="F7" s="8">
-        <v>11.83</v>
+        <v>12.76</v>
       </c>
       <c r="G7" s="8">
-        <v>31.41</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H7" s="8">
-        <v>4.79</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="I7" s="8">
         <f t="shared" si="0"/>
-        <v>2.395</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J7" s="8">
         <f t="shared" si="1"/>
-        <v>75.226950000000002</v>
+        <v>65.927999999999983</v>
       </c>
     </row>
     <row r="8" spans="2:10">
       <c r="F8" s="8">
-        <v>11.68</v>
+        <v>12.45</v>
       </c>
       <c r="G8" s="8">
-        <v>28.94</v>
+        <v>32.03</v>
       </c>
       <c r="H8" s="8">
-        <v>4.4800000000000004</v>
+        <v>3.71</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" si="0"/>
-        <v>2.2400000000000002</v>
+        <v>1.855</v>
       </c>
       <c r="J8" s="8">
         <f t="shared" si="1"/>
-        <v>64.825600000000009</v>
+        <v>59.415649999999999</v>
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="8">
+        <v>11.68</v>
+      </c>
+      <c r="G9" s="8">
+        <v>28.32</v>
+      </c>
+      <c r="H9" s="8">
+        <v>3.09</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="0"/>
+        <v>1.5449999999999999</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="1"/>
+        <v>43.754399999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="E10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="11">
-        <f>AVERAGE(F2:F8)</f>
-        <v>11.37142857142857</v>
-      </c>
-      <c r="G9" s="11">
-        <f t="shared" ref="G9:J9" si="2">AVERAGE(G2:G8)</f>
-        <v>28.54</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="F10" s="11">
+        <f>AVERAGE(F2:F9)</f>
+        <v>12.181250000000002</v>
+      </c>
+      <c r="G10" s="11">
+        <f t="shared" ref="G10:J10" si="2">AVERAGE(G2:G9)</f>
+        <v>29.477500000000003</v>
+      </c>
+      <c r="H10" s="11">
         <f t="shared" si="2"/>
-        <v>4.6785714285714288</v>
-      </c>
-      <c r="I9" s="11">
+        <v>3.9575</v>
+      </c>
+      <c r="I10" s="11">
         <f t="shared" si="2"/>
-        <v>2.3392857142857144</v>
-      </c>
-      <c r="J9" s="11">
+        <v>1.97875</v>
+      </c>
+      <c r="J10" s="11">
         <f t="shared" si="2"/>
-        <v>66.721171428571424</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="13.8">
-      <c r="E10" s="13" t="s">
+        <v>58.480312500000004</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" ht="13.8">
+      <c r="E11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="12">
-        <f>STDEV(F2:F8)</f>
-        <v>1.1013238786634409</v>
-      </c>
-      <c r="G10" s="12">
-        <f t="shared" ref="G10:J10" si="3">STDEV(G2:G8)</f>
-        <v>2.6841385955274371</v>
-      </c>
-      <c r="H10" s="12">
+      <c r="F11" s="12">
+        <f>STDEV(F2:F9)</f>
+        <v>0.54700319925938279</v>
+      </c>
+      <c r="G11" s="12">
+        <f t="shared" ref="G11:J11" si="3">STDEV(G2:G9)</f>
+        <v>3.0504039545139396</v>
+      </c>
+      <c r="H11" s="12">
         <f t="shared" si="3"/>
-        <v>0.14769660021234635</v>
-      </c>
-      <c r="I10" s="12">
+        <v>0.5194433834128882</v>
+      </c>
+      <c r="I11" s="12">
         <f t="shared" si="3"/>
-        <v>7.3848300106173173E-2</v>
-      </c>
-      <c r="J10" s="12">
+        <v>0.2597216917064441</v>
+      </c>
+      <c r="J11" s="12">
         <f t="shared" si="3"/>
-        <v>6.1989447481578885</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="E11" s="14" t="s">
+        <v>10.436800312381909</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="E12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="16">
-        <f>F10/F9</f>
-        <v>9.6850089832212161E-2</v>
-      </c>
-      <c r="G11" s="16">
-        <f t="shared" ref="G11:J11" si="4">G10/G9</f>
-        <v>9.4048303977835923E-2</v>
-      </c>
-      <c r="H11" s="16">
+      <c r="F12" s="16">
+        <f>F11/F10</f>
+        <v>4.4905342165983186E-2</v>
+      </c>
+      <c r="G12" s="16">
+        <f t="shared" ref="G12:J12" si="4">G11/G10</f>
+        <v>0.10348245117509759</v>
+      </c>
+      <c r="H12" s="16">
         <f t="shared" si="4"/>
-        <v>3.1568738976684711E-2</v>
-      </c>
-      <c r="I11" s="16">
+        <v>0.13125543484848723</v>
+      </c>
+      <c r="I12" s="16">
         <f t="shared" si="4"/>
-        <v>3.1568738976684711E-2</v>
-      </c>
-      <c r="J11" s="16">
+        <v>0.13125543484848723</v>
+      </c>
+      <c r="J12" s="16">
         <f t="shared" si="4"/>
-        <v>9.2908212122657194E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" ht="13.8">
-      <c r="B12" s="9" t="s">
+        <v>0.1784669039239814</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="13.8">
+      <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J13" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="7">
+    <row r="14" spans="2:10">
+      <c r="B14" s="7">
         <v>45</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C14" s="7">
         <v>10.199999999999999</v>
       </c>
-      <c r="D13" s="7">
-        <f>B13-C13</f>
+      <c r="D14" s="7">
+        <f>B14-C14</f>
         <v>34.799999999999997</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E14" s="7">
         <f>Оборудование!$I$2</f>
         <v>1</v>
       </c>
-      <c r="F13" s="8">
-        <v>9.83</v>
-      </c>
-      <c r="G13" s="8">
-        <v>23.84</v>
-      </c>
-      <c r="H13" s="8">
-        <v>4.79</v>
-      </c>
-      <c r="I13" s="8">
-        <f>H13/2</f>
-        <v>2.395</v>
-      </c>
-      <c r="J13" s="8">
-        <f>I13*G13</f>
-        <v>57.096800000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
       <c r="F14" s="8">
-        <v>12.14</v>
+        <v>11.37</v>
       </c>
       <c r="G14" s="8">
-        <v>27.39</v>
+        <v>29.71</v>
       </c>
       <c r="H14" s="8">
-        <v>4.79</v>
+        <v>3.71</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" ref="I14:I19" si="5">H14/2</f>
-        <v>2.395</v>
+        <f>H14/2</f>
+        <v>1.855</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" ref="J14:J19" si="6">I14*G14</f>
-        <v>65.599050000000005</v>
+        <f>I14*G14</f>
+        <v>55.112050000000004</v>
       </c>
     </row>
     <row r="15" spans="2:10">
@@ -2712,21 +2708,21 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="8">
-        <v>9.83</v>
+        <v>10.75</v>
       </c>
       <c r="G15" s="8">
-        <v>31.87</v>
+        <v>26</v>
       </c>
       <c r="H15" s="8">
-        <v>4.63</v>
+        <v>4.17</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="5"/>
-        <v>2.3149999999999999</v>
+        <f t="shared" ref="I15:I23" si="5">H15/2</f>
+        <v>2.085</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="6"/>
-        <v>73.779049999999998</v>
+        <f t="shared" ref="J15:J23" si="6">I15*G15</f>
+        <v>54.21</v>
       </c>
     </row>
     <row r="16" spans="2:10">
@@ -2738,153 +2734,1031 @@
         <v>11.68</v>
       </c>
       <c r="G16" s="8">
-        <v>28.32</v>
+        <v>28.47</v>
       </c>
       <c r="H16" s="8">
-        <v>4.4800000000000004</v>
+        <v>3.55</v>
       </c>
       <c r="I16" s="8">
         <f t="shared" si="5"/>
-        <v>2.2400000000000002</v>
+        <v>1.7749999999999999</v>
       </c>
       <c r="J16" s="8">
         <f t="shared" si="6"/>
-        <v>63.436800000000005</v>
+        <v>50.534249999999993</v>
       </c>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="8">
-        <v>12.61</v>
+        <v>12.3</v>
       </c>
       <c r="G17" s="8">
-        <v>28.01</v>
+        <v>28.17</v>
       </c>
       <c r="H17" s="8">
-        <v>4.79</v>
+        <v>4.32</v>
       </c>
       <c r="I17" s="8">
         <f t="shared" si="5"/>
-        <v>2.395</v>
+        <v>2.16</v>
       </c>
       <c r="J17" s="8">
         <f t="shared" si="6"/>
-        <v>67.083950000000002</v>
+        <v>60.847200000000008</v>
       </c>
     </row>
     <row r="18" spans="2:10">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
       <c r="F18" s="8">
-        <v>11.83</v>
+        <v>12.61</v>
       </c>
       <c r="G18" s="8">
-        <v>31.41</v>
+        <v>28.17</v>
       </c>
       <c r="H18" s="8">
-        <v>4.79</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="I18" s="8">
         <f t="shared" si="5"/>
-        <v>2.395</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="J18" s="8">
         <f t="shared" si="6"/>
-        <v>75.226950000000002</v>
+        <v>56.621699999999997</v>
       </c>
     </row>
     <row r="19" spans="2:10">
       <c r="F19" s="8">
-        <v>11.68</v>
+        <v>11.99</v>
       </c>
       <c r="G19" s="8">
-        <v>28.94</v>
+        <v>27.7</v>
       </c>
       <c r="H19" s="8">
-        <v>4.4800000000000004</v>
+        <v>4.63</v>
       </c>
       <c r="I19" s="8">
         <f t="shared" si="5"/>
-        <v>2.2400000000000002</v>
+        <v>2.3149999999999999</v>
       </c>
       <c r="J19" s="8">
         <f t="shared" si="6"/>
-        <v>64.825600000000009</v>
+        <v>64.125500000000002</v>
       </c>
     </row>
     <row r="20" spans="2:10">
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="8">
+        <v>10.91</v>
+      </c>
+      <c r="G20" s="8">
+        <v>25.39</v>
+      </c>
+      <c r="H20" s="8">
+        <v>3.24</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="5"/>
+        <v>1.62</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="6"/>
+        <v>41.131800000000005</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="F21" s="8">
+        <v>12.45</v>
+      </c>
+      <c r="G21" s="8">
+        <v>34.19</v>
+      </c>
+      <c r="H21" s="8">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="5"/>
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="6"/>
+        <v>68.721899999999991</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="F22" s="8">
+        <v>12.3</v>
+      </c>
+      <c r="G22" s="8">
+        <v>28.63</v>
+      </c>
+      <c r="H22" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="5"/>
+        <v>1.855</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="6"/>
+        <v>53.108649999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="F23" s="8">
+        <v>11.53</v>
+      </c>
+      <c r="G23" s="8">
+        <v>27.39</v>
+      </c>
+      <c r="H23" s="8">
+        <v>3.55</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="5"/>
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="6"/>
+        <v>48.617249999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="E24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="11">
-        <f>AVERAGE(F13:F19)</f>
-        <v>11.37142857142857</v>
-      </c>
-      <c r="G20" s="11">
-        <f t="shared" ref="G20" si="7">AVERAGE(G13:G19)</f>
-        <v>28.54</v>
-      </c>
-      <c r="H20" s="11">
-        <f t="shared" ref="H20" si="8">AVERAGE(H13:H19)</f>
-        <v>4.6785714285714288</v>
-      </c>
-      <c r="I20" s="11">
-        <f t="shared" ref="I20" si="9">AVERAGE(I13:I19)</f>
-        <v>2.3392857142857144</v>
-      </c>
-      <c r="J20" s="11">
-        <f t="shared" ref="J20" si="10">AVERAGE(J13:J19)</f>
-        <v>66.721171428571424</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" ht="13.8">
-      <c r="E21" s="13" t="s">
+      <c r="F24" s="11">
+        <f>AVERAGE(F14:F23)</f>
+        <v>11.788999999999998</v>
+      </c>
+      <c r="G24" s="11">
+        <f t="shared" ref="G24:J24" si="7">AVERAGE(G14:G23)</f>
+        <v>28.381999999999998</v>
+      </c>
+      <c r="H24" s="11">
+        <f t="shared" si="7"/>
+        <v>3.8919999999999995</v>
+      </c>
+      <c r="I24" s="11">
+        <f t="shared" si="7"/>
+        <v>1.9459999999999997</v>
+      </c>
+      <c r="J24" s="11">
+        <f t="shared" si="7"/>
+        <v>55.30303</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="13.8">
+      <c r="E25" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="12">
-        <f>STDEV(F13:F19)</f>
-        <v>1.1013238786634409</v>
-      </c>
-      <c r="G21" s="12">
-        <f t="shared" ref="G21:J21" si="11">STDEV(G13:G19)</f>
-        <v>2.6841385955274371</v>
-      </c>
-      <c r="H21" s="12">
+      <c r="F25" s="12">
+        <f>STDEV(F14:F23)</f>
+        <v>0.64809892934815305</v>
+      </c>
+      <c r="G25" s="12">
+        <f t="shared" ref="G25:J25" si="8">STDEV(G14:G23)</f>
+        <v>2.3974699627361797</v>
+      </c>
+      <c r="H25" s="12">
+        <f t="shared" si="8"/>
+        <v>0.416754657375834</v>
+      </c>
+      <c r="I25" s="12">
+        <f t="shared" si="8"/>
+        <v>0.208377328687917</v>
+      </c>
+      <c r="J25" s="12">
+        <f t="shared" si="8"/>
+        <v>7.9210684511553122</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="E26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="16">
+        <f>F25/F24</f>
+        <v>5.4974885855301824E-2</v>
+      </c>
+      <c r="G26" s="16">
+        <f t="shared" ref="G26:J26" si="9">G25/G24</f>
+        <v>8.4471494705664854E-2</v>
+      </c>
+      <c r="H26" s="16">
+        <f t="shared" si="9"/>
+        <v>0.10707981946963877</v>
+      </c>
+      <c r="I26" s="16">
+        <f t="shared" si="9"/>
+        <v>0.10707981946963877</v>
+      </c>
+      <c r="J26" s="16">
+        <f t="shared" si="9"/>
+        <v>0.14323027962763182</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" ht="13.8">
+      <c r="B27" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="7">
+        <v>40</v>
+      </c>
+      <c r="C28" s="7">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D28" s="7">
+        <f>B28-C28</f>
+        <v>29.8</v>
+      </c>
+      <c r="E28" s="7">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F28" s="8">
+        <v>11.22</v>
+      </c>
+      <c r="G28" s="8">
+        <v>26.78</v>
+      </c>
+      <c r="H28" s="8">
+        <v>4.17</v>
+      </c>
+      <c r="I28" s="8">
+        <f>H28/2</f>
+        <v>2.085</v>
+      </c>
+      <c r="J28" s="8">
+        <f>I28*G28</f>
+        <v>55.836300000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
+        <v>10.91</v>
+      </c>
+      <c r="G29" s="8">
+        <v>25.85</v>
+      </c>
+      <c r="H29" s="8">
+        <v>2.93</v>
+      </c>
+      <c r="I29" s="8">
+        <f t="shared" ref="I29:I34" si="10">H29/2</f>
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="J29" s="8">
+        <f t="shared" ref="J29:J34" si="11">I29*G29</f>
+        <v>37.870250000000006</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="8">
+        <v>11.37</v>
+      </c>
+      <c r="G30" s="8">
+        <v>26.93</v>
+      </c>
+      <c r="H30" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="I30" s="8">
+        <f t="shared" si="10"/>
+        <v>1.93</v>
+      </c>
+      <c r="J30" s="8">
         <f t="shared" si="11"/>
-        <v>0.14769660021234635</v>
-      </c>
-      <c r="I21" s="12">
+        <v>51.974899999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="8">
+        <v>11.53</v>
+      </c>
+      <c r="G31" s="8">
+        <v>29.56</v>
+      </c>
+      <c r="H31" s="8">
+        <v>3.24</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="10"/>
+        <v>1.62</v>
+      </c>
+      <c r="J31" s="8">
         <f t="shared" si="11"/>
-        <v>7.3848300106173173E-2</v>
-      </c>
-      <c r="J21" s="12">
+        <v>47.8872</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="F32" s="8">
+        <v>11.68</v>
+      </c>
+      <c r="G32" s="8">
+        <v>28.01</v>
+      </c>
+      <c r="H32" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="I32" s="8">
+        <f t="shared" si="10"/>
+        <v>1.7</v>
+      </c>
+      <c r="J32" s="8">
         <f t="shared" si="11"/>
-        <v>6.1989447481578885</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="E22" s="14" t="s">
+        <v>47.617000000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="F33" s="8">
+        <v>11.22</v>
+      </c>
+      <c r="G33" s="8">
+        <v>27.86</v>
+      </c>
+      <c r="H33" s="8">
+        <v>3.09</v>
+      </c>
+      <c r="I33" s="8">
+        <f t="shared" si="10"/>
+        <v>1.5449999999999999</v>
+      </c>
+      <c r="J33" s="8">
+        <f t="shared" si="11"/>
+        <v>43.043699999999994</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="F34" s="8">
+        <v>10.75</v>
+      </c>
+      <c r="G34" s="8">
+        <v>26</v>
+      </c>
+      <c r="H34" s="8">
+        <v>3.24</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="10"/>
+        <v>1.62</v>
+      </c>
+      <c r="J34" s="8">
+        <f t="shared" si="11"/>
+        <v>42.120000000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="E35" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="11">
+        <f>AVERAGE(F28:F34)</f>
+        <v>11.24</v>
+      </c>
+      <c r="G35" s="11">
+        <f t="shared" ref="G35:J35" si="12">AVERAGE(G28:G34)</f>
+        <v>27.284285714285716</v>
+      </c>
+      <c r="H35" s="11">
+        <f t="shared" si="12"/>
+        <v>3.4185714285714286</v>
+      </c>
+      <c r="I35" s="11">
+        <f t="shared" si="12"/>
+        <v>1.7092857142857143</v>
+      </c>
+      <c r="J35" s="11">
+        <f t="shared" si="12"/>
+        <v>46.621335714285713</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="13.8">
+      <c r="E36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="12">
+        <f>STDEV(F28:F34)</f>
+        <v>0.32771939216347851</v>
+      </c>
+      <c r="G36" s="12">
+        <f t="shared" ref="G36:J36" si="13">STDEV(G28:G34)</f>
+        <v>1.2989336285694391</v>
+      </c>
+      <c r="H36" s="12">
+        <f t="shared" si="13"/>
+        <v>0.44164195797911149</v>
+      </c>
+      <c r="I36" s="12">
+        <f t="shared" si="13"/>
+        <v>0.22082097898955574</v>
+      </c>
+      <c r="J36" s="12">
+        <f t="shared" si="13"/>
+        <v>6.1347776216633862</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="E37" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="16">
-        <f>F21/F20</f>
-        <v>9.6850089832212161E-2</v>
-      </c>
-      <c r="G22" s="16">
-        <f t="shared" ref="G22" si="12">G21/G20</f>
-        <v>9.4048303977835923E-2</v>
-      </c>
-      <c r="H22" s="16">
-        <f t="shared" ref="H22" si="13">H21/H20</f>
-        <v>3.1568738976684711E-2</v>
-      </c>
-      <c r="I22" s="16">
-        <f t="shared" ref="I22" si="14">I21/I20</f>
-        <v>3.1568738976684711E-2</v>
-      </c>
-      <c r="J22" s="16">
-        <f t="shared" ref="J22" si="15">J21/J20</f>
-        <v>9.2908212122657194E-2</v>
+      <c r="F37" s="16">
+        <f>F36/F35</f>
+        <v>2.9156529551910899E-2</v>
+      </c>
+      <c r="G37" s="16">
+        <f t="shared" ref="G37:J37" si="14">G36/G35</f>
+        <v>4.7607389915629475E-2</v>
+      </c>
+      <c r="H37" s="16">
+        <f t="shared" si="14"/>
+        <v>0.12918903910797244</v>
+      </c>
+      <c r="I37" s="16">
+        <f t="shared" si="14"/>
+        <v>0.12918903910797244</v>
+      </c>
+      <c r="J37" s="16">
+        <f t="shared" si="14"/>
+        <v>0.13158734145370202</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="13.8">
+      <c r="B38" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39" s="7">
+        <v>35</v>
+      </c>
+      <c r="C39" s="7">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D39" s="7">
+        <f>B39-C39</f>
+        <v>24.8</v>
+      </c>
+      <c r="E39" s="7">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F39" s="8">
+        <v>9.98</v>
+      </c>
+      <c r="G39" s="8">
+        <v>21.37</v>
+      </c>
+      <c r="H39" s="8">
+        <v>3.09</v>
+      </c>
+      <c r="I39" s="8">
+        <f>H39/2</f>
+        <v>1.5449999999999999</v>
+      </c>
+      <c r="J39" s="8">
+        <f>I39*G39</f>
+        <v>33.016649999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="8">
+        <v>9.98</v>
+      </c>
+      <c r="G40" s="8">
+        <v>22.45</v>
+      </c>
+      <c r="H40" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="I40" s="8">
+        <f>H40/2</f>
+        <v>1.7</v>
+      </c>
+      <c r="J40" s="8">
+        <f>I40*G40</f>
+        <v>38.164999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8">
+        <v>10.75</v>
+      </c>
+      <c r="G41" s="8">
+        <v>25.08</v>
+      </c>
+      <c r="H41" s="8">
+        <v>2.93</v>
+      </c>
+      <c r="I41" s="8">
+        <f>H41/2</f>
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="J41" s="8">
+        <f>I41*G41</f>
+        <v>36.742199999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
+        <v>11.06</v>
+      </c>
+      <c r="G42" s="8">
+        <v>25.08</v>
+      </c>
+      <c r="H42" s="8">
+        <v>3.24</v>
+      </c>
+      <c r="I42" s="8">
+        <f t="shared" ref="I42:I46" si="15">H42/2</f>
+        <v>1.62</v>
+      </c>
+      <c r="J42" s="8">
+        <f t="shared" ref="J42:J46" si="16">I42*G42</f>
+        <v>40.629599999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="F43" s="8">
+        <v>10.91</v>
+      </c>
+      <c r="G43" s="8">
+        <v>26.93</v>
+      </c>
+      <c r="H43" s="8">
+        <v>2.93</v>
+      </c>
+      <c r="I43" s="8">
+        <f t="shared" si="15"/>
+        <v>1.4650000000000001</v>
+      </c>
+      <c r="J43" s="8">
+        <f t="shared" si="16"/>
+        <v>39.452449999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="F44" s="8">
+        <v>10.75</v>
+      </c>
+      <c r="G44" s="8">
+        <v>25.39</v>
+      </c>
+      <c r="H44" s="8">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="I44" s="8">
+        <f t="shared" si="15"/>
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="J44" s="8">
+        <f t="shared" si="16"/>
+        <v>31.356650000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="F45" s="8">
+        <v>9.83</v>
+      </c>
+      <c r="G45" s="8">
+        <v>22.45</v>
+      </c>
+      <c r="H45" s="8">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="I45" s="8">
+        <f t="shared" si="15"/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="J45" s="8">
+        <f t="shared" si="16"/>
+        <v>26.041999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="F46" s="8">
+        <v>10.44</v>
+      </c>
+      <c r="G46" s="8">
+        <v>27.08</v>
+      </c>
+      <c r="H46" s="8">
+        <v>2.78</v>
+      </c>
+      <c r="I46" s="8">
+        <f t="shared" si="15"/>
+        <v>1.39</v>
+      </c>
+      <c r="J46" s="8">
+        <f t="shared" si="16"/>
+        <v>37.641199999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="E47" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="11">
+        <f>AVERAGE(F39:F46)</f>
+        <v>10.4625</v>
+      </c>
+      <c r="G47" s="11">
+        <f t="shared" ref="G47:J47" si="17">AVERAGE(G39:G46)</f>
+        <v>24.478749999999998</v>
+      </c>
+      <c r="H47" s="11">
+        <f t="shared" si="17"/>
+        <v>2.895</v>
+      </c>
+      <c r="I47" s="11">
+        <f t="shared" si="17"/>
+        <v>1.4475</v>
+      </c>
+      <c r="J47" s="11">
+        <f t="shared" si="17"/>
+        <v>35.38071875</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="13.8">
+      <c r="E48" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="12">
+        <f>STDEV(F39:F46)</f>
+        <v>0.47640768855496618</v>
+      </c>
+      <c r="G48" s="12">
+        <f t="shared" ref="G48:J48" si="18">STDEV(G39:G46)</f>
+        <v>2.1455764293741</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="18"/>
+        <v>0.36625518036317001</v>
+      </c>
+      <c r="I48" s="12">
+        <f t="shared" si="18"/>
+        <v>0.183127590181585</v>
+      </c>
+      <c r="J48" s="12">
+        <f t="shared" si="18"/>
+        <v>4.896631447881699</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="E49" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" s="16">
+        <f>F48/F47</f>
+        <v>4.5534785047069648E-2</v>
+      </c>
+      <c r="G49" s="16">
+        <f t="shared" ref="G49:J49" si="19">G48/G47</f>
+        <v>8.76505715926712E-2</v>
+      </c>
+      <c r="H49" s="16">
+        <f t="shared" si="19"/>
+        <v>0.12651301566948878</v>
+      </c>
+      <c r="I49" s="16">
+        <f t="shared" si="19"/>
+        <v>0.12651301566948878</v>
+      </c>
+      <c r="J49" s="16">
+        <f t="shared" si="19"/>
+        <v>0.13839830339460527</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="13.8">
+      <c r="B50" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="7">
+        <v>30</v>
+      </c>
+      <c r="C51" s="7">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D51" s="7">
+        <f>B51-C51</f>
+        <v>19.8</v>
+      </c>
+      <c r="E51" s="7">
+        <f>Оборудование!$I$2</f>
+        <v>1</v>
+      </c>
+      <c r="F51" s="8">
+        <v>10.29</v>
+      </c>
+      <c r="G51" s="8">
+        <v>22.92</v>
+      </c>
+      <c r="H51" s="8">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="I51" s="8">
+        <f>H51/2</f>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="J51" s="8">
+        <f>I51*G51</f>
+        <v>26.587199999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8">
+        <v>10.91</v>
+      </c>
+      <c r="G52" s="8">
+        <v>21.53</v>
+      </c>
+      <c r="H52" s="8">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="I52" s="8">
+        <f>H52/2</f>
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="J52" s="8">
+        <f>I52*G52</f>
+        <v>26.589550000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8">
+        <v>10.91</v>
+      </c>
+      <c r="G53" s="8">
+        <v>24.15</v>
+      </c>
+      <c r="H53" s="8">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="I53" s="8">
+        <f>H53/2</f>
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="J53" s="8">
+        <f>I53*G53</f>
+        <v>24.270749999999996</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8">
+        <v>10.91</v>
+      </c>
+      <c r="G54" s="8">
+        <v>23.38</v>
+      </c>
+      <c r="H54" s="8">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="I54" s="8">
+        <f t="shared" ref="I54:I58" si="20">H54/2</f>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="J54" s="8">
+        <f t="shared" ref="J54:J58" si="21">I54*G54</f>
+        <v>27.120799999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="F55" s="8">
+        <v>9.98</v>
+      </c>
+      <c r="G55" s="8">
+        <v>22.45</v>
+      </c>
+      <c r="H55" s="8">
+        <v>2.63</v>
+      </c>
+      <c r="I55" s="8">
+        <f t="shared" si="20"/>
+        <v>1.3149999999999999</v>
+      </c>
+      <c r="J55" s="8">
+        <f t="shared" si="21"/>
+        <v>29.521749999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="F56" s="8">
+        <v>9.67</v>
+      </c>
+      <c r="G56" s="8">
+        <v>20.29</v>
+      </c>
+      <c r="H56" s="8">
+        <v>3.24</v>
+      </c>
+      <c r="I56" s="8">
+        <f t="shared" si="20"/>
+        <v>1.62</v>
+      </c>
+      <c r="J56" s="8">
+        <f t="shared" si="21"/>
+        <v>32.869799999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="E57" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="11">
+        <f>AVERAGE(F51:F56)</f>
+        <v>10.445</v>
+      </c>
+      <c r="G57" s="11">
+        <f t="shared" ref="G57:J57" si="22">AVERAGE(G51:G56)</f>
+        <v>22.453333333333333</v>
+      </c>
+      <c r="H57" s="11">
+        <f t="shared" si="22"/>
+        <v>2.4983333333333335</v>
+      </c>
+      <c r="I57" s="11">
+        <f t="shared" si="22"/>
+        <v>1.2491666666666668</v>
+      </c>
+      <c r="J57" s="11">
+        <f t="shared" si="22"/>
+        <v>27.826641666666664</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="13.8">
+      <c r="E58" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" s="12">
+        <f>STDEV(F51:F56)</f>
+        <v>0.54581132271142929</v>
+      </c>
+      <c r="G58" s="12">
+        <f t="shared" ref="G58:J58" si="23">STDEV(G51:G56)</f>
+        <v>1.3775146702183123</v>
+      </c>
+      <c r="H58" s="12">
+        <f t="shared" si="23"/>
+        <v>0.41720099073068678</v>
+      </c>
+      <c r="I58" s="12">
+        <f t="shared" si="23"/>
+        <v>0.20860049536534339</v>
+      </c>
+      <c r="J58" s="12">
+        <f t="shared" si="23"/>
+        <v>2.9838239786248559</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="E59" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" s="16">
+        <f>F58/F57</f>
+        <v>5.2255751336661493E-2</v>
+      </c>
+      <c r="G59" s="16">
+        <f t="shared" ref="G59:J59" si="24">G58/G57</f>
+        <v>6.1350118923024596E-2</v>
+      </c>
+      <c r="H59" s="16">
+        <f t="shared" si="24"/>
+        <v>0.16699172410834692</v>
+      </c>
+      <c r="I59" s="16">
+        <f t="shared" si="24"/>
+        <v>0.16699172410834692</v>
+      </c>
+      <c r="J59" s="16">
+        <f t="shared" si="24"/>
+        <v>0.1072290366321552</v>
       </c>
     </row>
   </sheetData>
